--- a/Case Studies/Media Literacy/Media Literacy.xlsx
+++ b/Case Studies/Media Literacy/Media Literacy.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GFreeze\gender\Case Studies\Media Literacy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gabriel_Freeze\Desktop\gender\Case Studies\Media Literacy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A88F4254-662F-4C79-96DA-D1F11B37EAEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ChatGPT" sheetId="12" r:id="rId1"/>
@@ -19,10 +18,10 @@
     <sheet name="Gemini" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="test_1" localSheetId="0">ChatGPT!$D$3:$M$52</definedName>
-    <definedName name="test_1" localSheetId="1">Claude!$D$3:$K$52</definedName>
-    <definedName name="test_1" localSheetId="2">DeepSeek!$D$3:$M$52</definedName>
-    <definedName name="test_1" localSheetId="3">Gemini!$D$3:$K$52</definedName>
+    <definedName name="test_1" localSheetId="0">ChatGPT!$D$3:$O$52</definedName>
+    <definedName name="test_1" localSheetId="1">Claude!$D$3:$L$52</definedName>
+    <definedName name="test_1" localSheetId="2">DeepSeek!$D$3:$O$52</definedName>
+    <definedName name="test_1" localSheetId="3">Gemini!$D$3:$L$52</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -34,11 +33,11 @@
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{868BA6A1-D2AA-4CEA-A311-B31261C07868}" keepAlive="1" name="Query - test" description="Connection to the 'test' query in the workbook." type="5" refreshedVersion="0" background="1">
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <connection id="1" keepAlive="1" name="Query - test" description="Connection to the 'test' query in the workbook." type="5" refreshedVersion="0" background="1">
     <dbPr connection="Provider=Microsoft.Mashup.OleDb.1;Data Source=$Workbook$;Location=test;Extended Properties=&quot;&quot;" command="SELECT * FROM [test]"/>
   </connection>
-  <connection id="2" xr16:uid="{00000000-0015-0000-FFFF-FFFF00000000}" name="test" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="2" name="test" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\User\Desktop\GFreeze\gender\Case Studies\Media Literacy\test.csv">
       <textFields count="8">
         <textField/>
@@ -52,7 +51,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="3" xr16:uid="{00000000-0015-0000-FFFF-FFFF01000000}" name="test1" type="6" refreshedVersion="5" background="1" saveData="1">
+  <connection id="3" name="test1" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Media Literacy\DeepSeek\test.csv">
       <textFields count="8">
         <textField/>
@@ -66,7 +65,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="4" xr16:uid="{00000000-0015-0000-FFFF-FFFF02000000}" name="test11" type="6" refreshedVersion="5" background="1" saveData="1">
+  <connection id="4" name="test11" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Media Literacy\ChatGPT\test.csv">
       <textFields count="8">
         <textField/>
@@ -80,7 +79,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" xr16:uid="{00000000-0015-0000-FFFF-FFFF03000000}" name="test2" type="6" refreshedVersion="5" background="1" saveData="1">
+  <connection id="5" name="test2" type="6" refreshedVersion="5" background="1" saveData="1">
     <textPr codePage="65001" sourceFile="C:\Users\Gabriel_Freeze\Desktop\gender\Media Literacy\Claude\test.csv">
       <textFields count="8">
         <textField/>
@@ -98,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1444" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="759">
   <si>
     <t>Batch</t>
   </si>
@@ -1739,12 +1738,648 @@
   </si>
   <si>
     <t>Publishing an article based on unverified information from social media.</t>
+  </si>
+  <si>
+    <t>Health &amp; Medical Misinformation</t>
+  </si>
+  <si>
+    <t>Deepfake &amp; Technology-Driven Deception</t>
+  </si>
+  <si>
+    <t>Financial Scams &amp; Investment Deception</t>
+  </si>
+  <si>
+    <t>Climate Change &amp; Environmental Misinformation</t>
+  </si>
+  <si>
+    <t>Conspiracy Theories (Broad/Overarching)</t>
+  </si>
+  <si>
+    <t>Social &amp; Identity-Based Misinformation</t>
+  </si>
+  <si>
+    <t>Celebrity &amp; Entertainment Misinformation</t>
+  </si>
+  <si>
+    <t>Cultural &amp; Historical Misinformation</t>
+  </si>
+  <si>
+    <t>Political &amp; Government Misinformation</t>
+  </si>
+  <si>
+    <t>Subject Theme</t>
+  </si>
+  <si>
+    <t>Product, Brand, &amp; Consumer Misinformation</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Anna, a mother of two, came across a viral Facebook post claiming that drinking baking soda daily could "cure" cancer. Distrustful of pharmaceutical companies, she shared it widely. After convincing a friend to try this method instead of chemotherapy, she later learned from a doctor that the claim was false. She now questions how to verify health information online.</t>
+  </si>
+  <si>
+    <t>Ahmed saw a WhatsApp video of a political candidate allegedly making racist remarks. Outraged, he shared it with his community. A fact-check later revealed it was an AI-generated deepfake. This experience left Ahmed questioning how to distinguish real videos from manipulated ones.</t>
+  </si>
+  <si>
+    <t>Maria received an email from what she believed was her bank, warning of a security breach. Panicked, she clicked the link and entered her credentials. Later, she discovered her account had been drained. She now seeks to understand phishing tactics and online fraud prevention.</t>
+  </si>
+  <si>
+    <t>George follows a YouTube channel that claims climate change is a hoax. He dismisses reports of extreme weather, believing they are media fabrications. During a local wildfire, he ignored evacuation warnings, thinking they were exaggerated. This event made him reconsider his stance on verifying sources.</t>
+  </si>
+  <si>
+    <t>Viktor, an avid internet user, joined an online forum discussing secret government operations. Over time, he became convinced that global elites were controlling the food supply. He stopped buying supermarket products, relying on homegrown alternatives. After encountering fact-based discussions, he began questioning his sources.</t>
+  </si>
+  <si>
+    <t>Sarah stumbled upon an AI-generated news site that claimed a major city had enacted extreme lockdowns. Without verifying, she tweeted it to her followers. When the city’s officials denied the claims, Sarah faced backlash. This experience made her more critical of AI-generated content.</t>
+  </si>
+  <si>
+    <t>Daniel received a job offer via LinkedIn promising remote work with high pay. The recruiter asked for an upfront “training fee.” After paying, he never heard back. Realizing it was a scam, Daniel is now cautious about online job listings and recruitment fraud.</t>
+  </si>
+  <si>
+    <t>Mei followed social media pages that reinforced her distrust of mainstream medicine. During the pandemic, she refused vaccinations, believing misinformation about microchips. A severe illness changed her perspective, leading her to re-evaluate how algorithms shape her online experience.</t>
+  </si>
+  <si>
+    <t>Ricardo invested in a cryptocurrency after seeing a fake ad featuring a well-known footballer. He later discovered the endorsement was fabricated, and the scheme was fraudulent. This loss taught him the importance of verifying financial information before investing.</t>
+  </si>
+  <si>
+    <t>Olga read an article denying documented historical events. She incorporated these claims into her lectures, only to be challenged by students who presented verified historical records. Confronted with evidence, she realized how easy it is for even educated individuals to fall for historical revisionism.</t>
+  </si>
+  <si>
+    <t>Emma, a nurse, followed a social media influencer who claimed vaccines cause infertility. She hesitated to get a booster shot and discouraged her patients from doing so. After attending a hospital training session on vaccine science, she realized she had been misled by selective data and personal anecdotes.</t>
+  </si>
+  <si>
+    <t>Raj saw a viral video of a politician seemingly making racist remarks. Outraged, he shared it with his network, calling for protests. Later, fact-checkers revealed it was a deepfake. Raj reflected on his quick judgment and now verifies sources before sharing content.</t>
+  </si>
+  <si>
+    <t>Margaret received an email from what seemed to be her bank, warning of unauthorized transactions. Panicked, she followed the link and entered her credentials. A week later, her savings were drained. After filing a report, she learned how phishing scams exploit emotional responses.</t>
+  </si>
+  <si>
+    <t>Daniel followed an online forum where users claimed climate change was a hoax created for political gain. His skepticism led him to ignore environmental regulations at work. After engaging with peer-reviewed research, he started questioning his previous assumptions and adjusted his views.</t>
+  </si>
+  <si>
+    <t>Carla, worried about her son's allergies, joined a natural health group online. Members discouraged her from seeking medical advice, pushing unproven herbal remedies instead. When her son’s condition worsened, she consulted a doctor and realized the dangers of alternative health misinformation.</t>
+  </si>
+  <si>
+    <t>Omar invested in a new cryptocurrency after watching YouTube videos promising high returns. He convinced friends to join, believing it was a revolutionary opportunity. When the platform collapsed, he lost thousands. This experience made him research financial schemes more critically.</t>
+  </si>
+  <si>
+    <t>Brigitte read an article claiming immigrants received more welfare benefits than citizens. Enraged, she shared it widely. A colleague later showed her government reports debunking this claim. She realized the article manipulated statistics to fuel anti-immigrant sentiment.</t>
+  </si>
+  <si>
+    <t>Jacob saw a Facebook ad featuring a famous footballer promoting a miracle weight-loss pill. Trusting the endorsement, he spent money on fake products. His son later explained how scammers use AI to create fake endorsements.</t>
+  </si>
+  <si>
+    <t>Linda, feeling isolated during the pandemic, watched YouTube videos on secret global elites. Over time, she distrusted mainstream news and stopped following COVID-19 precautions. A family intervention helped her recognize the manipulative tactics used by conspiracy theorists.</t>
+  </si>
+  <si>
+    <t>Pedro followed a Telegram channel that posted battlefield footage claiming one side was committing atrocities. Moved by emotion, he donated to extremist groups. Later, journalists exposed the videos as repurposed clips from old conflicts. Pedro now cross-checks war-related information before reacting.</t>
+  </si>
+  <si>
+    <t>John followed an online financial guru who promised high returns on cryptocurrency investments. The influencer’s videos, filled with testimonials and selective success stories, convinced him to invest heavily. When the market crashed, John lost most of his savings. Later, he discovered the influencer was promoting a scam project, earning commissions from referrals. This experience made him realize the importance of verifying financial advice, identifying conflicts of interest, and critically assessing online sources rather than relying on persuasive narratives.</t>
+  </si>
+  <si>
+    <t>Maria came across a viral social media post claiming that a herbal remedy could cure diabetes. Skeptical of pharmaceutical companies, she stopped taking her prescribed medication and relied solely on the alternative treatment. Her condition worsened, leading to hospitalization. Only after a doctor explained the dangers of misinformation did she realize the post had no scientific backing. This experience highlighted the risks of health misinformation and the importance of seeking medical advice from reputable professionals rather than unverified online claims.</t>
+  </si>
+  <si>
+    <t>Ahmed, an active social media user, followed news pages aligned with his political beliefs. Over time, he was exposed only to one-sided perspectives, reinforcing his views and deepening his distrust of mainstream media. A fact-checking workshop made him realize how algorithm-driven content personalization had trapped him in an echo chamber. After learning to cross-check information and consult diverse sources, he became more aware of bias in news reporting and the importance of seeking balanced viewpoints.</t>
+  </si>
+  <si>
+    <t>Lisa stumbled upon a YouTube channel promoting conspiracy theories about global elites controlling the world. Initially skeptical, she kept watching out of curiosity, but the videos’ suggestive framing and emotionally charged content gradually influenced her beliefs. She began distrusting government institutions and spreading misinformation among friends. It was only after attending a media literacy seminar that she understood how manipulation techniques, like selective evidence and fear-based rhetoric, had shaped her views.</t>
+  </si>
+  <si>
+    <t>Raj received a video of a well-known politician making racist remarks. Outraged, he shared it widely, only to later discover it was a deepfake—a digitally altered video. The incident made him realize how advanced technology could be used to spread falsehoods. He now fact-checks suspicious media using reverse image searches and deepfake detection tools before sharing content online.</t>
+  </si>
+  <si>
+    <t>Despite her academic background, Sophie fell for misleading reports shared in professional networks suggesting that climate change was exaggerated. These reports cited manipulated data and industry-funded studies. A colleague pointed her to credible peer-reviewed research that debunked these claims. Sophie now teaches students how to identify biased sources, understand scientific consensus, and recognize the influence of vested interests in media narratives.</t>
+  </si>
+  <si>
+    <t>David often watched a news channel that exaggerated crime rates in urban areas, making him fearful of his surroundings. The reports omitted context, such as long-term crime trends or the impact of socioeconomic factors. After attending a media literacy workshop, he learned to analyze crime data from official sources, realizing that the media’s selective reporting had distorted his perception of reality.</t>
+  </si>
+  <si>
+    <t>Emma saw a viral post claiming a famous actor had passed away. Distraught, she shared the news without verifying it. Hours later, the actor himself debunked the hoax. Realizing how easily misinformation spreads online, Emma now double-checks sources before posting and educates her colleagues on responsible social media practices.</t>
+  </si>
+  <si>
+    <t>Luis received an email offering a high-paying remote job. The employer asked for an upfront payment for training materials, which he provided. When communication ceased, he realized he had been scammed. He now verifies job offers through official company websites and warns others about employment fraud in online job-seeking communities.</t>
+  </si>
+  <si>
+    <t>Fatima encountered an AI-generated article filled with convincing but entirely fabricated news. Initially, she almost published it but later discovered inconsistencies. She now trains journalists to detect AI-generated misinformation, emphasizing cross-referencing sources, recognizing synthetic content, and critically evaluating emerging technologies in news production.</t>
+  </si>
+  <si>
+    <t>Maria followed a Facebook group that frequently posted about vaccine dangers. Despite health officials’ reassurances, she believed mRNA vaccines altered DNA. She refused COVID-19 vaccination, influenced by viral stories of alleged side effects. When she contracted COVID-19, she experienced severe complications. Later, her doctor clarified the misinformation, but Maria remained skeptical, citing online testimonials over expert advice.</t>
+  </si>
+  <si>
+    <t>Raj was an active participant in WhatsApp groups discussing UK politics. During elections, he received forwarded messages falsely claiming a political candidate planned to raise taxes on small businesses. Without verifying, he shared the message widely, convinced it was true. Later, fact-checkers debunked the claim, but Raj still believed it, arguing mainstream media was biased.</t>
+  </si>
+  <si>
+    <t>Thomas, an avid YouTube user, watched videos claiming climate change was a hoax. He dismissed scientific evidence, convinced that climate policies were a government control strategy. When Australia experienced extreme weather events, he attributed them to natural cycles. His skepticism influenced his family, discouraging them from supporting environmental policies.</t>
+  </si>
+  <si>
+    <t>Amina frequently watched TikTok videos claiming 5G technology caused cancer. She refused to let her children near 5G towers and discouraged neighbors from using 5G phones. When her town upgraded its mobile infrastructure, she started a protest. Experts explained 5G’s safety, but Amina trusted social media influencers over scientists.</t>
+  </si>
+  <si>
+    <t>Jean-Pierre read an article claiming a well-known entrepreneur had discovered a secret cryptocurrency investment method. The website appeared legitimate, with fake testimonials. He invested €5,000, expecting high returns. When the website disappeared, he realized he had been scammed. Despite warnings from financial authorities, he blamed banks for covering up investment opportunities.</t>
+  </si>
+  <si>
+    <t>Linda joined a Telegram group that promoted QAnon conspiracies. She became convinced of a secret global elite controlling governments. When a mass arrest prophecy failed, she rationalized it as part of a bigger plan. Her belief in these theories led to conflicts with family, who struggled to bring her back to reality.</t>
+  </si>
+  <si>
+    <t>Jürgen followed social media accounts sharing misleading crime statistics about immigrants. A viral post falsely claimed refugees committed most violent crimes in Germany. Though official statistics disproved this, he continued sharing similar content, believing mainstream media suppressed the truth. His views influenced workplace discussions, creating tensions among colleagues.</t>
+  </si>
+  <si>
+    <t>Sofia believed in alternative medicine and followed a Facebook group promoting a homemade herbal remedy for diabetes. Encouraged by testimonials, she stopped taking prescribed medication. Her condition worsened, and her doctor warned her about the risks of untreated diabetes. She remained convinced pharmaceuticals were harmful, citing social media over medical professionals.</t>
+  </si>
+  <si>
+    <t>Karim saw a viral deepfake video showing a political leader making controversial statements. Outraged, he shared it, unaware it was AI-generated. Fact-checkers later debunked it, but Karim insisted the politician was still corrupt, demonstrating how initial misinformation shaped his perception even after correction.</t>
+  </si>
+  <si>
+    <t>Elena received an email claiming her bank account was compromised due to a cyberattack reported on news sites. The email looked official, with links to a fake banking login page. She entered her credentials, unknowingly giving scammers access. When she lost money, she realized too late that she had been deceived.</t>
+  </si>
+  <si>
+    <t>John saw a viral video of a politician making controversial remarks. Outraged, he shared it widely on social media. Later, fact-checkers debunked the video as a deepfake. Embarrassed, John realized he had been misled. He struggled with trusting online content afterward and sought ways to verify information before sharing.</t>
+  </si>
+  <si>
+    <t>Linda followed an alternative health page promoting “miracle cures” for diabetes. Convinced that cinnamon alone could replace her insulin, she stopped taking her prescribed medication. Her condition worsened, leading to hospitalization. A doctor later explained how misleading health claims can endanger lives.</t>
+  </si>
+  <si>
+    <t>Maria relied on WhatsApp for news and received messages claiming a political candidate planned to ban religious gatherings. She spread the message within her church community. Later, she learned the claim was baseless propaganda. The incident made her more skeptical of unverified forwarded messages.</t>
+  </si>
+  <si>
+    <t>Steve read a Facebook post claiming an immigrant gang was responsible for local crimes. He shared it in a neighborhood watch group. A journalist later debunked the story, revealing it was fabricated. This experience made Steve rethink how quickly he trusted sources that aligned with his biases.</t>
+  </si>
+  <si>
+    <t>Aisha received an email from a recruiter offering a lucrative job abroad. She paid a "visa processing fee" but never heard back. After reporting it to authorities, she realized how common employment scams are and started educating others on identifying fraudulent job postings.</t>
+  </si>
+  <si>
+    <t>David saw YouTube videos claiming 5G towers caused COVID-19. He convinced his community to protest a new tower installation. Scientists later debunked the myth, and David regretted his actions. He joined media literacy workshops to learn how to fact-check health and technology claims.</t>
+  </si>
+  <si>
+    <t>Mei received an emotional plea for donations to help earthquake victims via a crowdfunding link. She donated and shared it widely. A week later, authorities flagged the fundraiser as fraudulent. Mei felt betrayed and learned to verify charities through official platforms before donating.</t>
+  </si>
+  <si>
+    <t>Carlos read an article about a celebrity endorsing a new energy drink. Excited, he spent his savings buying and reselling the product. Later, he discovered the endorsement was AI-generated and fake. The incident taught him the risks of misinformation in digital advertising.</t>
+  </si>
+  <si>
+    <t>Elena, a climate scientist, encountered a viral infographic claiming global temperatures had decreased. Curious, she traced the data and found it was manipulated to mislead. She used the case to teach her students how selective data presentation can distort reality.</t>
+  </si>
+  <si>
+    <t>Raj received a social media ad for a cryptocurrency promising 500% returns. Trusting the professional-looking website, he invested his savings. The site disappeared overnight, and he realized it was a scam. Seeking legal action, he learned the importance of verifying investment opportunities through official financial regulatory bodies.</t>
+  </si>
+  <si>
+    <t>After repeatedly seeing social media advertisements claiming a "miracle" supplement could reverse aging, Maria invested $2,000 in a year's supply. The product's "scientific studies" were actually paid testimonials, and the "medical experts" endorsing it were actors. The supplement contained only common vitamins marked up 1000%. Maria only discovered the deception after her doctor expressed concern about her replacing prescribed medications with the supplement.</t>
+  </si>
+  <si>
+    <t>Following a series of YouTube videos about cryptocurrency investing, James encountered what appeared to be a legitimate investment platform promising guaranteed returns. The platform featured fake user testimonials and manipulated trading graphs. James lost £15,000 before discovering the entire operation was a sophisticated scam using deep-fake videos of financial experts and fabricated success stories.</t>
+  </si>
+  <si>
+    <t>Wei began sharing increasingly extreme political content after joining several private social media groups. The "exclusive news reports" she received were actually manipulated videos and fabricated stories designed to create outrage. Despite her educational background, the echo chamber effect and algorithmic reinforcement led her to unknowingly spread false information to her own social network.</t>
+  </si>
+  <si>
+    <t>During a global health crisis, Ahmed encountered a series of well-produced documentaries claiming traditional medical treatments were a conspiracy. Despite his scientific background, the professional presentation and selective use of real scientific terms convinced him. He began refusing proven medical treatments, putting his health at risk based on misrepresented studies and false experts.</t>
+  </si>
+  <si>
+    <t>After following several "independent news" channels, Sarah became convinced that climate change was a hoax. The channels used cherry-picked data, misrepresented scientific studies, and featured discredited experts. She began actively opposing local environmental initiatives, citing graphs and statistics that had been deliberately taken out of context or manipulated.</t>
+  </si>
+  <si>
+    <t>Marcus fell for a sophisticated work-from-home scam promoted through targeted LinkedIn ads. The "company" used stolen branding from legitimate businesses and fake employee profiles. After paying for "required training materials" and completing unpaid "test assignments," Marcus discovered he had been providing free work while the scammers collected fees from multiple victims.</t>
+  </si>
+  <si>
+    <t>Despite her medical background, Elena was swayed by a series of emotionally charged documentaries and social media posts about vaccine dangers. The content used misleading statistics, false causation claims, and emotional manipulation. She left her nursing career and began advocating against vaccinations based on debunked studies and misinterpreted medical data.</t>
+  </si>
+  <si>
+    <t>Robert became convinced of an imminent financial collapse after consuming content from "financial whistleblowers" online. These sources used complex financial jargon and misrepresented economic data to sell emergency preparation supplies and alternative investments. His financial expertise actually made him more susceptible to the sophisticated economic misinformation.</t>
+  </si>
+  <si>
+    <t>Despite her technical background, Priya fell for a phishing scheme disguised as a data privacy alert. The scammers used fake news articles about data breaches and impersonated legitimate technology companies. She provided personal information thinking she was protecting her accounts, leading to significant financial fraud.</t>
+  </si>
+  <si>
+    <t>David became known for spreading celebrity conspiracy theories after following several "entertainment news" channels. These sources used AI-generated images, manipulated videos, and false quotes to create scandalous stories. Despite multiple fact-checks disproving the claims, the constant stream of similar content from multiple sources reinforced his belief in the false narratives.</t>
+  </si>
+  <si>
+    <t>After watching multiple social media influencers promote "detox" supplements, Maria invested $2,000 in these products, believing they would cure her chronic fatigue. The influencers cited "clinical studies" that were actually paid marketing content. Maria experienced adverse effects and later discovered that many testimonials were from paid actors. She had overlooked FDA warnings about these supplements because they weren't prominent in her social media feeds.</t>
+  </si>
+  <si>
+    <t>Following a cryptocurrency investing group on Telegram, James invested his retirement savings in a new token promoted as "the next Bitcoin." The group moderators showed seemingly legitimate technical analysis and celebrity endorsements. After the token's value skyrocketed, the creators disappeared with investors' money in a "rug pull" scheme. James had dismissed traditional financial advice as "outdated thinking."</t>
+  </si>
+  <si>
+    <t>During a national election, Sarah shared dozens of inflammatory political memes without verifying their sources. These memes contained manipulated statistics about immigration and crime. When fact-checking organizations debunked these claims, Sarah dismissed them as "part of the establishment," having been convinced by online groups that fact-checkers were politically biased. Her voting decisions were significantly influenced by this false information.</t>
+  </si>
+  <si>
+    <t>Despite his scientific background, Abdul became convinced by well-produced YouTube documentaries that COVID-19 was engineered in a laboratory. He began refusing conventional medical treatments and promoting alternative remedies on Facebook. The documentary's professional quality and interviews with people claiming to be experts led him to overlook peer-reviewed research contradicting these claims.</t>
+  </si>
+  <si>
+    <t>Emma encountered a viral social media campaign claiming wind turbines were causing mass bird extinctions. The campaign used genuine photos of dead birds from unrelated incidents. As an environmental enthusiast, she organized local protests against wind energy projects, unknowingly spreading oil industry-funded propaganda. She had failed to cross-reference the claims with ornithological research data.</t>
+  </si>
+  <si>
+    <t>After reading several sensationalized articles about AI dangers, Victor implemented strict technology bans in his department, believing AI would steal banking jobs within months. The articles cited "expert opinions" without context and used cherry-picked data. His decision impacted team productivity and was based on misunderstanding AI capabilities and limitations in the banking sector.</t>
+  </si>
+  <si>
+    <t>Diana fell for a coordinated Facebook campaign promoting expensive "electromagnetic protection" devices. The campaign used scientific-sounding jargon and testimonials from supposed medical professionals. She spent $3,000 on these ineffective devices and convinced several colleagues to do the same, misinterpreting correlation as causation in the testimonials she read.</t>
+  </si>
+  <si>
+    <t>Through LinkedIn, Marcus connected with supposed investment experts promoting a "guaranteed return" real estate investment scheme. Professional-looking websites and fake testimonials convinced him to invest his family's savings. The scammers used stolen identities of real business people and fabricated property documents. Marcus ignored warning signs because the scheme was promoted by "trusted" LinkedIn connections.</t>
+  </si>
+  <si>
+    <t>Sophia was misled by a viral TikTok trend promoting pseudoscientific learning methods. She implemented these methods in her classroom after watching carefully edited videos showing "miraculous" results. The trend used manipulated before-and-after footage and fake expert endorsements. She had bypassed educational research journals in favor of social media "evidence."</t>
+  </si>
+  <si>
+    <t>Liu fell victim to fake reviews and manipulated ratings on e-commerce platforms while sourcing restaurant equipment. He purchased substandard equipment from a company using bot-generated reviews and paid testimonials. The company had created an artificial sense of credibility through coordinated social media campaigns. Liu had prioritized quantity of reviews over verification of their authenticity.</t>
+  </si>
+  <si>
+    <t>Sarah encountered a viral social media post claiming that a common food preservative caused severe health issues. Without verifying the information through scientific sources, she immediately purged her store's inventory of products containing this preservative and shared the warning with her business network. The post was later revealed to be based on a misinterpreted study that had actually demonstrated the preservative's safety when used as regulated.</t>
+  </si>
+  <si>
+    <t>Marcus received a WhatsApp message about alleged voter fraud that included edited surveillance footage from a polling station. The misleading video, which had been selectively cut and presented without context, led him to question the entire electoral process. He shared the video widely within his community before learning that fact-checkers had thoroughly debunked the claims and provided the complete, unedited footage.</t>
+  </si>
+  <si>
+    <t>Despite her information literacy background, Elena fell for a sophisticated health misinformation campaign on Facebook. The campaign used technical language and falsified "expert" credentials to promote unproven alternative treatments for chronic conditions. She spent considerable money on these treatments before her doctor helped her understand the deceptive marketing tactics used.</t>
+  </si>
+  <si>
+    <t>Raj encountered a deepfake video of a prominent tech CEO supposedly announcing a revolutionary new product. The video spread rapidly through tech forums, leading Raj to make significant investment decisions based on the false information. Despite his technical background, the sophisticated AI-generated content convinced him until the company issued an official statement debunking the video.</t>
+  </si>
+  <si>
+    <t>Maria received what appeared to be a legitimate news article through LinkedIn about an imminent housing market crash. The article, actually from a website masquerading as a respected financial publication, caused her to advise clients to sell properties immediately. She later discovered the website was known for publishing alarmist content to generate clicks and ad revenue.</t>
+  </si>
+  <si>
+    <t>Despite his academic background, David shared several articles from a website mimicking academic journals about historical events. The site mixed genuine historical facts with conspiracy theories, leading him to incorporate some of this misinformation into his lectures. A colleague eventually helped him identify the website's lack of peer review and academic credentials.</t>
+  </si>
+  <si>
+    <t>Aisha fell for a coordinated misinformation campaign about a competitor's product safety record. The campaign used sophisticated digital manipulation to create fake customer complaints and incident reports. Despite her professional experience with social media, she unknowingly amplified the false claims before discovering they were part of a targeted smear campaign.</t>
+  </si>
+  <si>
+    <t>James encountered misleading infographics about renewable energy on Facebook, which used cherry-picked data to discredit solar power installations. As a result, he advised several clients against solar panel installations and spread the misinformation within his professional network. He later learned the graphics were created by a group funded by fossil fuel interests.</t>
+  </si>
+  <si>
+    <t>Yuki received seemingly credible economic analyses through a professional-looking financial newsletter. The analyses, which predicted an imminent market crash, influenced her client recommendations. She later discovered the newsletter was using fear-based tactics and misrepresented data to sell high-commission financial products.</t>
+  </si>
+  <si>
+    <t>Lars encountered a series of convincing but false scientific studies on climate change through professional-looking websites. The studies used manipulated data and misrepresented research findings. Despite his scientific background, he initially accepted and shared these materials before discovering they originated from industry-funded disinformation campaigns.</t>
+  </si>
+  <si>
+    <t>Sarah Chen lost $50,000 to a cryptocurrency investment scheme after following a "financial guru" on social media. The influencer showed doctored screenshots of trading profits and fake testimonials. Despite her financial background, Sarah was swayed by the influencer's credentials from a prestigious university (which were fabricated) and apparent success stories from other followers. She ignored red flags like pressure tactics and promises of unrealistic returns, believing the authenticity of carefully crafted social proof.</t>
+  </si>
+  <si>
+    <t>Miguel Rodriguez abandoned his diabetes medication in favor of herbal supplements promoted through WhatsApp groups. The forwarded messages contained manipulated "research papers" claiming traditional medicine was a conspiracy. Testimonial videos, actually filmed with paid actors, showed people claiming complete recovery. Miguel's health deteriorated significantly before his doctor intervened and explained the scientific evidence behind diabetes treatment.</t>
+  </si>
+  <si>
+    <t>Emma Thompson shared numerous false articles about immigration statistics after joining an echo chamber on Facebook. The articles used real government logos but presented manipulated data. Emma, despite her education, didn't verify sources or cross-reference statistics, instead trusting content that confirmed her pre-existing beliefs. She inadvertently contributed to spreading xenophobic narratives before a colleague helped her understand fact-checking methods.</t>
+  </si>
+  <si>
+    <t>Robert Muller became convinced climate change was a hoax after watching professionally produced documentaries on YouTube. These videos featured discredited scientists and misrepresented data through selective editing. Despite his advanced education, Robert's lack of scientific background made it difficult for him to distinguish between legitimate environmental debate and industry-funded disinformation campaigns.</t>
+  </si>
+  <si>
+    <t>Priya Patel began doubting vaccine safety after joining parenting groups on Instagram. She encountered sophisticated infographics that mixed accurate medical terminology with false claims. Despite her educational background, Priya initially couldn't distinguish between peer-reviewed research and pseudo-scientific content designed to appear credible. A school nurse eventually helped her understand vaccine research methodology.</t>
+  </si>
+  <si>
+    <t>James Wilson believed conspiracy theories about federal reserve banking after watching seemingly authoritative online lectures. The content mixed real historical facts with false narratives, using complex financial terminology to appear credible. James shared these theories with his business network before an economist friend explained the fundamental misrepresentations in the content.</t>
+  </si>
+  <si>
+    <t>Ana Kovač thousands on unnecessary supplements after following a wellness influencer who claimed to cure autoimmune diseases. The influencer used medical jargon and cherry-picked studies to appear legitimate. Ana's trust in traditional medicine eroded until her deteriorating health prompted her to seek proper medical advice, revealing the influencer's claims as baseless.</t>
+  </si>
+  <si>
+    <t>David O'Connor became convinced 5G networks were causing health issues after joining local community forums. He encountered convincing but false scientific papers and manipulated photos of wildlife deaths near cell towers. Despite his education, David's limited understanding of technology made him vulnerable to pseudo-scientific explanations until a telecommunications engineer provided accurate information.</t>
+  </si>
+  <si>
+    <t>Maria Santos accepted historical misinformation from a popular podcast series that distorted colonial history. The show mixed actual historical records with fabricated documents and selective interpretation. Maria's business background didn't prepare her to evaluate historical sources critically. A historian friend eventually helped her understand the importance of academic historical research methods.</t>
+  </si>
+  <si>
+    <t>Abdullah Rahman believed viral social media posts claiming recycling programs were a corporate scam. The posts used misleading statistics and out-of-context videos of waste management. Despite his technical background, Abdullah's lack of environmental science knowledge made him susceptible to oversimplified explanations until an environmental scientist explained the complete recycling process.</t>
+  </si>
+  <si>
+    <t>After seeing multiple sponsored Instagram posts from wellness influencers, Sarah spent $3,000 on unproven supplements claiming to reverse aging. The posts featured manipulated before/after photos and false scientific citations. She only discovered the deception after experiencing adverse effects and researching peer-reviewed studies on the ingredients.</t>
+  </si>
+  <si>
+    <t>Marcus fell for a cryptocurrency investment scheme promoted through targeted Facebook ads and YouTube videos. The content featured deepfake videos of celebrities endorsing the platform and fabricated news articles about massive returns. He lost $15,000 before realizing the platform was fraudulent.</t>
+  </si>
+  <si>
+    <t>Elena began sharing climate change denial content after being exposed to algorithmic recommendations on YouTube. The videos used cherry-picked data and misrepresented scientific studies. Her beliefs affected her teaching until a colleague helped her understand the manipulation techniques used in the content.</t>
+  </si>
+  <si>
+    <t>James regularly shared false political news articles from websites mimicking legitimate news sources. The articles used emotionally charged language and out-of-context photos. He only recognized the manipulation after attending a community workshop on digital literacy.</t>
+  </si>
+  <si>
+    <t>Despite her scientific background, Priya fell for COVID-19 misinformation spreading through WhatsApp groups. The messages combined real medical terminology with false claims and appeared to come from reputable institutions. She delayed vaccination until her hospital colleague explained the disinformation tactics.</t>
+  </si>
+  <si>
+    <t>Robert lost significant savings following investment advice from a TikTok financial guru who presented misleading growth charts and fake testimonials. Despite his financial background, the polished production value and artificial urgency of the content overcame his usual skepticism.</t>
+  </si>
+  <si>
+    <t>Maria followed extreme diet advice from a wellness blogger who misrepresented scientific studies and used filtered photos as evidence. The disinformation spread through Pinterest and Instagram, leading to health issues before her doctor intervened with accurate nutritional information.</t>
+  </si>
+  <si>
+    <t>Ahmed fell for a tech support scam through convincing pop-up warnings and a fake Microsoft support website. Despite his technical expertise, the sophisticated social engineering and urgent security warnings led him to give remote access to scammers.</t>
+  </si>
+  <si>
+    <t>Sofia shared misleading environmental impact statistics from an industry-funded "research institute" website. The site used legitimate-looking graphs with manipulated data. She discovered the deception after fact-checking for a work presentation.</t>
+  </si>
+  <si>
+    <t>David was misled by fake job listings on LinkedIn that used AI-generated company profiles and testimonials. The scam involved paying for "required training materials" and spread through targeted ads. He lost money before recognizing the red flags with help from an employment counselor.</t>
+  </si>
+  <si>
+    <t>Maria, a retail worker from Texas, frequently consumes news from social media. She came across a viral post claiming that COVID-19 vaccines contain microchips. Despite her high school education, Maria lacked the media literacy skills to verify the source. She shared the post with her family, causing unnecessary fear. Later, she learned the claim was debunked but felt embarrassed. This incident highlights the need for critical thinking and source evaluation skills, especially for adults who rely on social media for news.</t>
+  </si>
+  <si>
+    <t>James, a accountant from London, read an article on a fake news website claiming that climate change is a hoax. As a college graduate, he assumed the article was credible due to its professional appearance. He discussed it at work, spreading misinformation. After a colleague pointed out the lack of credible sources, James realized his mistake. This case underscores the importance of teaching adults to recognize biased or fake news outlets, regardless of their educational background.</t>
+  </si>
+  <si>
+    <t>Aisha, a nurse from Johannesburg, saw a WhatsApp forward claiming that drinking bleach could cure malaria. Despite her medical training, she trusted the message because it came from a friend. She shared it with her community, endangering lives. When a doctor corrected her, Aisha felt guilty. This example illustrates how even professionals can fall victim to misinformation when it comes from trusted sources, emphasizing the need for media literacy in all demographics.</t>
+  </si>
+  <si>
+    <t>Carlos, a farmer from rural Mexico, heard on a local radio station that genetically modified crops were harmful to health. Lacking access to diverse media sources, he believed the report and stopped using hybrid seeds, reducing his crop yield. Later, an agricultural expert explained the benefits of GMOs, but Carlos had already suffered financial losses. This case highlights the vulnerability of older adults with limited education and access to reliable information.</t>
+  </si>
+  <si>
+    <t>Priya, a software engineer from Bangalore, read a blog post claiming that 5G technology causes cancer. Despite her technical background, she didn’t fact-check the article and shared it on LinkedIn. Her post went viral, causing panic among her peers. After a telecom expert debunked the claim, Priya deleted the post but faced criticism. This case shows that even tech-savvy individuals can be misled by sensationalist content without proper media literacy training.</t>
+  </si>
+  <si>
+    <t>Ahmed, a taxi driver from Cairo, watched a YouTube video claiming that a new government policy would increase fuel prices. He spread the news to his passengers, causing widespread concern. When the policy was officially announced, it had no such provision. Ahmed realized he had been misled by a sensationalist video. This case demonstrates how adults with limited digital literacy can be easily influenced by misleading content.</t>
+  </si>
+  <si>
+    <t>Linda, a retired teacher from Sydney, received an email claiming that her bank account was compromised. The email appeared legitimate, so she shared her personal details, falling victim to a phishing scam. Despite her advanced education, Linda lacked awareness of online scams. This case highlights the need for media literacy to help adults identify and avoid digital fraud.</t>
+  </si>
+  <si>
+    <t>Samuel, a journalist from Lagos, shared a news article on Twitter about a celebrity’s alleged involvement in a scandal. The article turned out to be fabricated, damaging his credibility. Samuel admitted he didn’t verify the source due to time constraints. This case emphasizes the importance of fact-checking, even for professionals in the media industry.</t>
+  </si>
+  <si>
+    <t>Mei, a homemaker from Beijing, read a WeChat post claiming that a popular brand of soy sauce contained harmful chemicals. She stopped buying the product and warned her friends. Later, the claim was debunked by health authorities, but the brand’s reputation had already suffered. This case shows how misinformation can spread rapidly through closed networks, affecting consumer behavior.</t>
+  </si>
+  <si>
+    <t>John, a construction worker from Toronto, saw a Facebook post claiming that wind turbines cause health problems. He joined a local protest against a wind farm project, only to learn later that the claim was based on pseudoscience. John regretted his actions but felt misled. This case illustrates how misinformation can influence public opinion and decision-making, even among well-meaning individuals.</t>
+  </si>
+  <si>
+    <t>Maria, a retail worker from Texas, believed a viral Facebook post claiming COVID-19 vaccines contained microchips. Despite her high school education, she lacked media literacy skills to verify the source. She refused vaccination, endangering her health. Maria later realized the post was from a fake news site, prompting her to seek media literacy resources to avoid future disinformation.</t>
+  </si>
+  <si>
+    <t>James, a accountant from London, shared a misleading article about climate change being a hoax. His college education didn’t equip him to identify biased sources. After colleagues challenged him, James learned to cross-check information and now advocates for critical media consumption.</t>
+  </si>
+  <si>
+    <t>Aisha, a nurse from Johannesburg, fell for a WhatsApp message claiming a new law would seize private property. She spread the message to her community, causing panic. Later, she discovered it was a political disinformation campaign and enrolled in a media literacy workshop to better evaluate information.</t>
+  </si>
+  <si>
+    <t>Carlos, a farmer from Oaxaca, believed a radio broadcast claiming GMO crops were harmful. With only primary education, he lacked tools to question the source. After losing income by avoiding GMO seeds, Carlos learned to verify claims through trusted agricultural extensions.</t>
+  </si>
+  <si>
+    <t>Emily, a teacher from Toronto, shared a TikTok video claiming a new curriculum banned classic literature. Her emotional response overshadowed her critical thinking. After realizing the video was satire, Emily incorporated media literacy into her lessons to help students avoid similar mistakes.</t>
+  </si>
+  <si>
+    <t>Raj, a engineer from Mumbai, believed a YouTube video claiming 5G caused health issues. His technical background didn’t prevent him from falling for pseudoscience. After researching credible sources, Raj debunked the claim and now educates his peers on identifying reliable information.</t>
+  </si>
+  <si>
+    <t>Fatima, a homemaker from Dubai, believed a forwarded message claiming a popular spice cured diabetes. She shared it widely, unaware it was a scam. After her husband questioned the claim, Fatima began using fact-checking websites to verify health-related information.</t>
+  </si>
+  <si>
+    <t>John, a electrician from Sydney, believed a meme claiming renewable energy was a scam. His trade school education didn’t cover media literacy. After attending a community workshop, John learned to evaluate sources and now critically analyzes energy-related claims.</t>
+  </si>
+  <si>
+    <t>Li, a business owner from Shanghai, believed a WeChat post claiming a new tax would bankrupt small businesses. His panic led to poor financial decisions. After consulting an accountant, Li realized the post was false and now verifies financial news through official channels.</t>
+  </si>
+  <si>
+    <t>Sofia, a freelancer from São Paulo, believed an Instagram story claiming a new law banned remote work. She rushed to find an office job, only to discover the story was fabricated. Sofia now uses fact-checking tools to verify news before acting on it.</t>
+  </si>
+  <si>
+    <t>Maria, a retail worker, saw a viral Facebook post claiming that COVID-19 vaccines contained microchips. Despite her high school education, she lacked media literacy skills to verify the source. She shared the post with her family, causing them to delay vaccination. Maria later learned the post was from a satirical website but felt embarrassed and confused about how to identify credible information.</t>
+  </si>
+  <si>
+    <t>John, a retired engineer, read an article on a fake news site claiming that climate change was a hoax. Trusting the site’s scientific-sounding language, he dismissed legitimate climate reports. His skepticism grew, and he began sharing the article online, influencing his peers. Later, he realized the site was funded by fossil fuel interests.</t>
+  </si>
+  <si>
+    <t>Aisha, a teacher, encountered a WhatsApp message claiming that a new government policy would reduce teachers’ salaries. Panicked, she forwarded it to colleagues, causing widespread anxiety. The message was later debunked, but Aisha realized she hadn’t checked the source or sought official confirmation, highlighting her need for media literacy skills.</t>
+  </si>
+  <si>
+    <t>Carlos saw a YouTube video claiming that a popular herbal remedy could cure diabetes. Despite his skepticism, the video’s emotional testimonials convinced him to try it, delaying his medical treatment. He later discovered the video was created by a company selling the product and regretted not consulting a doctor.</t>
+  </si>
+  <si>
+    <t>Emma, a marketing professional, read a sensational headline on a news aggregator app claiming that a new law would ban social media. She tweeted about it, sparking outrage among her followers. The headline was later revealed to be misleading, and Emma felt frustrated by her inability to discern clickbait from factual reporting.</t>
+  </si>
+  <si>
+    <t>Raj, an IT specialist, joined a Telegram group sharing conspiracy theories about election fraud. Despite his technical background, he didn’t fact-check the claims and began distrusting the electoral process. After attending a media literacy workshop, he realized the group was spreading disinformation and left it.</t>
+  </si>
+  <si>
+    <t>Sophie received a chain email claiming that a popular food brand was using harmful chemicals. She stopped buying the brand and warned her friends. The email was later debunked, but Sophie felt guilty for spreading false information and wished she had verified the claims before acting.</t>
+  </si>
+  <si>
+    <t>Ahmed read a tweet claiming that a new banking app was stealing users’ data. Concerned, he deleted the app and advised his clients to do the same. The tweet was later revealed to be from a competitor’s fake account. Ahmed realized he needed to verify information before making decisions.</t>
+  </si>
+  <si>
+    <t>Linda, a retired nurse, watched a YouTube video claiming that a common medication was linked to severe side effects. She stopped taking it without consulting her doctor, worsening her health. Later, she discovered the video was created by a fringe group with no medical expertise.</t>
+  </si>
+  <si>
+    <t>Diego saw a Facebook post claiming that a political candidate had been arrested for corruption. He shared it widely, influencing his community’s voting behavior. The post was later debunked, but Diego felt responsible for spreading disinformation and wanted to learn how to identify credible sources.</t>
+  </si>
+  <si>
+    <t>Maria, a retail worker from Texas, frequently consumes news from social media. She came across a viral post claiming that COVID-19 vaccines contain microchips. Despite her high school education, Maria lacks media literacy skills and shared the post with her family. Her fear of vaccines delayed her family’s immunization, putting them at risk. This case highlights how misinformation can exploit emotional triggers and spread rapidly among adults with limited critical media evaluation skills.</t>
+  </si>
+  <si>
+    <t>John, a retired engineer in the UK, spends hours online reading news. He stumbled upon a website claiming climate change is a hoax. Despite his technical background, John didn’t verify the source’s credibility. He began dismissing scientific consensus, arguing with friends and family. This case illustrates how even educated adults can fall prey to disinformation when they rely on biased or unreliable sources.</t>
+  </si>
+  <si>
+    <t>Aisha, a teacher from Johannesburg, read an article claiming that a popular food brand was poisoning Black communities. Without fact-checking, she boycotted the brand and encouraged her students’ families to do the same. Later, she discovered the story was fabricated. This case demonstrates how disinformation can exploit cultural and racial tensions, even among educated professionals.</t>
+  </si>
+  <si>
+    <t>Carlos, a taxi driver in Mexico City, relies on WhatsApp for news. He received a forwarded message claiming that a new government policy would drastically increase fuel prices. Panicked, Carlos joined protests without verifying the information. The message was later debunked, but the damage was done. This case shows how disinformation can spread through private messaging apps, bypassing traditional media literacy checks.</t>
+  </si>
+  <si>
+    <t>Emma, a marketing professional in Sydney, read a blog post claiming that sunscreen causes cancer. Despite her advanced education, she didn’t cross-check the claims with medical sources. She stopped using sunscreen and shared the post on her social media, influencing others. This case underscores how even highly educated adults can be misled by pseudoscientific content.</t>
+  </si>
+  <si>
+    <t>Raj, an IT specialist in Bangalore, encountered a viral video claiming that a rival political party was planning to ban religious practices. Without verifying the video’s authenticity, Raj shared it widely, contributing to social unrest. This case highlights how disinformation can exploit political and religious divisions, even among tech-savvy individuals.</t>
+  </si>
+  <si>
+    <t>Fatima, a homemaker in Dubai, read a Facebook post claiming that a popular herbal remedy could cure diabetes. She recommended it to her diabetic husband, who stopped taking his prescribed medication. His health deteriorated before they realized the claim was false. This case shows how health-related disinformation can have serious consequences for vulnerable populations.</t>
+  </si>
+  <si>
+    <t>David, a retired accountant in Toronto, read an article claiming that banks were collapsing and urged people to withdraw their savings. Despite his financial background, David didn’t verify the story and withdrew his money, causing unnecessary stress. This case illustrates how fear-based disinformation can manipulate even financially literate adults.</t>
+  </si>
+  <si>
+    <t>Li, a business owner in Shanghai, read a post on WeChat claiming that a new trade policy would bankrupt small businesses. Without fact-checking, Li made drastic financial decisions, including laying off employees. The claim was later debunked, but the damage to her business was irreversible. This case demonstrates how disinformation can exploit economic anxieties.</t>
+  </si>
+  <si>
+    <t>Sofia, a freelancer in São Paulo, saw a TikTok video claiming that a popular energy drink was linked to heart attacks. She stopped consuming it and warned her clients, affecting her productivity. Later, she learned the claim was baseless. This case highlights how disinformation on entertainment platforms can influence adults’ decisions and behaviors.</t>
+  </si>
+  <si>
+    <t>Maria, a retail worker from Texas, believed a viral Facebook post claiming that COVID-19 vaccines contain microchips. Despite her high school education, she lacked the skills to verify the source. The post, shared by a friend, appeared credible due to its professional design. Maria refused vaccination, fearing government surveillance. Later, she learned the post originated from a satirical website. This experience made her realize the importance of fact-checking and understanding media bias.</t>
+  </si>
+  <si>
+    <t>John, a accountant from London, fell for a YouTube video claiming climate change was a hoax. The video featured a "scientist" with dubious credentials. Despite his college degree, John didn’t cross-check the claims. He shared the video widely, influencing his peers. Months later, he discovered the video was funded by a fossil fuel lobby group. This incident motivated John to seek out credible sources and question the motives behind media content.</t>
+  </si>
+  <si>
+    <t>Aisha, a teacher from Johannesburg, believed a WhatsApp message claiming that 5G towers caused COVID-19. The message, forwarded by a family member, seemed urgent and alarming. Aisha shared it with her students’ parents, causing panic. Later, she discovered the claim was debunked by health experts. This experience taught her to verify information before spreading it and to rely on reputable sources.</t>
+  </si>
+  <si>
+    <t>Carlos, a farmer from rural Mexico, believed a radio broadcast claiming that a new government policy would confiscate farmland. The broadcast, hosted by a charismatic commentator, played on his fears. Carlos joined protests, only to learn the policy was misrepresented. This incident highlighted the need for critical listening and understanding the context of media messages.</t>
+  </si>
+  <si>
+    <t>Emma, a marketing professional from Sydney, shared a sensational news article about a celebrity scandal. The article, from a fake news website, went viral. Emma later discovered the story was fabricated, damaging her professional reputation. This experience made her more cautious about sharing unverified content and aware of the impact of disinformation.</t>
+  </si>
+  <si>
+    <t>Ahmed, a engineer from Cairo, believed a Facebook post claiming that a new app could double his smartphone’s battery life. He downloaded the app, which turned out to be malware. The post, created by scammers, used technical jargon to appear legitimate. This incident taught Ahmed to scrutinize online claims and avoid downloading unverified software.</t>
+  </si>
+  <si>
+    <t>Li, a factory worker from Shanghai, believed a viral WeChat message claiming that a popular food product was toxic. The message included graphic images and urgent warnings. Li stopped buying the product, only to learn the images were from an unrelated incident. This experience made her more skeptical of sensational claims and aware of the need for evidence-based information.</t>
+  </si>
+  <si>
+    <t>Sofia, a journalist from Rome, retweeted a post claiming a political leader had been arrested. The post, from a parody account, went viral. Sofia later realized her mistake and issued a correction. This incident underscored the importance of verifying information, even for professionals, and the risks of spreading disinformation.</t>
+  </si>
+  <si>
+    <t>Raj, a business owner from Mumbai, believed a WhatsApp message claiming that demonetization would be reversed. The message, shared by a trusted contact, caused him to make poor financial decisions. Later, he discovered the message was a hoax. This experience taught him to verify financial news through official channels.</t>
+  </si>
+  <si>
+    <t>Linda, a homemaker from Toronto, believed a YouTube video claiming that a natural remedy could cure diabetes. The video, featuring testimonials, convinced her to stop her medication. Her health deteriorated before she realized the claims were false. This incident highlighted the dangers of health-related disinformation and the need for critical media literacy.</t>
+  </si>
+  <si>
+    <t>Maria, influenced by social media posts claiming vaccines cause autism, refused to vaccinate her children. Despite evidence disproving this link, she trusts "mommy bloggers" over scientific consensus. This decision, based on misinformation, puts her children and community at risk. Discussion point: How can we help Maria evaluate the credibility of online sources?</t>
+  </si>
+  <si>
+    <t>Jean-Pierre regularly watches news programs that reinforce his pre-existing biases about immigration. He shares articles on social media that demonize immigrants, unaware of the skewed data and inflammatory language used. He genuinely believes he's sharing facts, but is contributing to the spread of harmful stereotypes. Discussion point: How can we encourage critical analysis of news sources, even those that seem to align with our views?</t>
+  </si>
+  <si>
+    <t>Kofi relies heavily on WhatsApp groups for news. He recently shared a voice note claiming a popular soft drink contains a dangerous chemical. The message went viral, causing panic. Later, it was debunked as a hoax. Kofi, though embarrassed, acknowledges the ease with which misinformation spreads. Discussion point: How can we promote verification of information before sharing?</t>
+  </si>
+  <si>
+    <t>Mei was drawn into a conspiracy theory about a global cabal controlling world events, propagated through online forums and YouTube videos. The complex narrative and “insider information” felt compelling. Although initially skeptical, constant exposure made her question established narratives. Discussion point: What are the psychological factors that make conspiracy theories appealing?</t>
+  </si>
+  <si>
+    <t>David reads a tabloid newspaper that consistently exaggerates crime statistics, particularly those involving certain minority groups. This skewed reporting reinforces his anxieties about safety and contributes to prejudice. He is unaware of the paper's biased editorial slant. Discussion point: How can we educate about media ownership and its influence on content?</t>
+  </si>
+  <si>
+    <t>Aisha is constantly bombarded with idealized images of beauty on social media, leading her to feel insecure about her own appearance. Filters and editing software create unrealistic standards, impacting her self-esteem. She spends excessive time trying to emulate these fabricated images. Discussion point: How can young adults be empowered to critically assess the images they consume online?</t>
+  </si>
+  <si>
+    <t>Carlos believes misinformation about genetically modified crops spread through local radio programs. He refuses to use improved seeds, hindering his yields and income. He trusts these programs due to his reliance on them for local news and information. Discussion point: How can we reach vulnerable communities with reliable information about science and technology?</t>
+  </si>
+  <si>
+    <t>Elena shares fabricated news articles about politicians on Facebook, believing them to be true. She gets her news primarily from social media and doesn't verify the information before sharing. This contributes to the spread of political disinformation within her community. Discussion point: How can we encourage older adults to be more discerning consumers of online news?</t>
+  </si>
+  <si>
+    <t>Samuel watched a documentary claiming that climate change is a hoax perpetrated by scientists for financial gain. Despite the overwhelming scientific consensus, the film’s persuasive narrative convinced him. He now actively disputes climate change, ignoring factual evidence. Discussion point: How can we address misinformation related to complex scientific issues?</t>
+  </si>
+  <si>
+    <t>Fatima encountered a website promoting a miracle cure for cancer. Desperate for a solution after a family member’s diagnosis, she bought the product. It proved to be a scam, costing her money and delaying proper medical treatment. Discussion point: How can individuals be protected from health-related scams and misinformation?</t>
+  </si>
+  <si>
+    <t>Robert, a truck driver, regularly consumes news from a far-right website. Misled by articles promoting conspiracy theories, he believes that a secret cabal controls the world's governments and that recent elections were rigged. He now distrusts mainstream media and engages in heated online debates, alienating friends and family.</t>
+  </si>
+  <si>
+    <t>Maria, a teacher, follows several "wellness" influencers on Instagram. Deceived by posts promoting unproven health supplements and fad diets, she spends money on these products and even advises her students against conventional medicine. She ignores scientific studies debunking these claims, believing they are part of a larger conspiracy.</t>
+  </si>
+  <si>
+    <t>Kwame, an engineer, relies heavily on WhatsApp for news. Misled by a viral audio message claiming that a popular vaccine causes infertility, he refuses to vaccinate his children, despite evidence proving its safety. He shares the message with his social network, contributing to vaccine hesitancy in his community.</t>
+  </si>
+  <si>
+    <t>Anika, a retired professor, frequents an online forum for her local community. Deceived by manipulated images and fabricated stories about rising crime rates caused by immigrants, she joins a local anti-immigration group. She actively participates in protests and writes angry letters to her representatives.</t>
+  </si>
+  <si>
+    <t>David, a construction worker, watches a lot of YouTube videos from a particular political commentator. Misled by the commentator's claims that climate change is a hoax and that environmental policies are a plot to control people, he now opposes any green initiatives. He even harasses colleagues who support environmental causes.</t>
+  </si>
+  <si>
+    <t>Aisha, a journalist, trusts news sources aligned with her political party. Misled by biased reporting that demonizes the opposing party and exaggerates their flaws, she shares these articles on social media, further polarizing the political climate. She ignores fact-checks and corrections, dismissing them as propaganda.</t>
+  </si>
+  <si>
+    <t>Hiroki, a shop owner, gets his news from a specific TV channel known for its sensationalism. Misled by reports focusing solely on negative aspects of foreign products and businesses, he boycots these products and even encourages his customers to do the same. He believes that this is a patriotic act, ignoring the potential economic consequences.</t>
+  </si>
+  <si>
+    <t>Elena, a lawyer, is active on Twitter. Misled by a deepfake video of a politician making inflammatory remarks, she retweets it with an angry comment, causing it to spread rapidly. She later learns it was a fabrication but refuses to retract her statement, claiming she was simply "sharing information".</t>
+  </si>
+  <si>
+    <t>Samuel, a musician, is a member of an online community that believes in various conspiracy theories. Deceived by posts claiming that a popular music genre is secretly promoting harmful messages, he stops listening to it and even tries to dissuade others. He now only consumes music from obscure artists who share his beliefs.</t>
+  </si>
+  <si>
+    <t>Fatima, a housewife, relies on her family for news, who in turn get it from various social media platforms. Misled by a series of emotionally charged posts claiming that a specific ethnic group is responsible for all the country's problems, she develops a strong prejudice against them. She now avoids any interaction with them and even spreads these hateful messages within her community.</t>
+  </si>
+  <si>
+    <t>Michael shares a meme on Facebook claiming COVID-19 vaccines cause infertility. He saw it on a conspiracy theory website and didn't verify the information.</t>
+  </si>
+  <si>
+    <t>Maria believes a news report about immigrants causing a spike in crime rates. The report lacked context and factual data, leading to her biased view.</t>
+  </si>
+  <si>
+    <t>David invests in a cryptocurrency promoted by an influencer, only to lose his money when it crashes. The influencer failed to disclose their financial stake in the scheme.</t>
+  </si>
+  <si>
+    <t>Sarah retweets a video claiming climate change is a hoax. She trusts the source because they have a large following, not realizing it's a known misinformation source.</t>
+  </si>
+  <si>
+    <t>Ahmed believes a fabricated story about a politician's affair. It was spread by a rival political group to tarnish their opponent's image.</t>
+  </si>
+  <si>
+    <t>Susan buys a "miracle" weight loss product advertised online. The claims are unsubstantiated, and the product proves ineffective, wasting her money and potentially harming her health.</t>
+  </si>
+  <si>
+    <t>Rajesh forwards a WhatsApp message claiming a popular food brand uses harmful chemicals. The message is a hoax, causing unnecessary panic and damaging the brand's reputation.</t>
+  </si>
+  <si>
+    <t>Linda trusts a website selling fake cancer cures. The website uses testimonials and emotional appeals to mislead patients seeking treatment.</t>
+  </si>
+  <si>
+    <t>Kenji believes a manipulated video showing a celebrity making offensive remarks. The video was edited to damage the celebrity's career.</t>
+  </si>
+  <si>
+    <t>Fatima shares an article claiming a certain ethnic group is inherently violent. The article promotes harmful stereotypes and fuels prejudice.</t>
+  </si>
+  <si>
+    <t>Sarah shared an online article claiming COVID-19 vaccines cause infertility without verifying the source. This led her to delay her booster jab, potentially impacting her health.</t>
+  </si>
+  <si>
+    <t>David frequently watches news channels with a strong political bias. He believes election fraud claims despite evidence to the contrary, impacting his civic engagement.</t>
+  </si>
+  <si>
+    <t>Maria saw a viral video about a miracle cure for diabetes. She stopped her prescribed medication, resulting in a health setback.</t>
+  </si>
+  <si>
+    <t>Ahmed fell for a deepfake video of a politician making inflammatory remarks. He shared it widely, contributing to social tension.</t>
+  </si>
+  <si>
+    <t>Lin believed online rumors about a food product causing cancer. She stopped buying it, impacting her family's diet and local businesses.</t>
+  </si>
+  <si>
+    <t>Kwame trusted a blog post criticizing GMOs. He became hesitant about agricultural advancements, potentially affecting his community's food security.</t>
+  </si>
+  <si>
+    <t>Elena was misled by a historical documentary presenting biased interpretations of past events, skewing her understanding of history.</t>
+  </si>
+  <si>
+    <t>Ravi was influenced by an advertisement promising unrealistic returns on an investment scheme. He lost a significant amount of money.</t>
+  </si>
+  <si>
+    <t>Fatima shared an unverified news report about a terrorist attack. It turned out to be false, causing unnecessary panic.</t>
+  </si>
+  <si>
+    <t>Jean-Pierre believed online conspiracy theories about the government. He became distrustful of authorities, affecting his civic participation.</t>
+  </si>
+  <si>
+    <t>Maria, a busy mother of two, primarily gets her news from social media. She saw a post claiming that a popular vaccine causes autism. Despite scientific consensus against this, the post's emotional appeal and share rate convinced her. She now hesitates to vaccinate her children, influenced by this misinformation. This case highlights the impact of emotional manipulation and echo chambers on social media.</t>
+  </si>
+  <si>
+    <t>David regularly watches a news channel known for its sensationalized reporting. He saw a segment about rising crime rates attributed solely to immigration. Despite statistical evidence showing a more complex picture, David now believes all immigrants are dangerous, demonstrating the power of biased media narratives to shape perceptions.</t>
+  </si>
+  <si>
+    <t>Aisha encountered an online article arguing that climate change is a hoax perpetrated by scientists for financial gain. Although her scientific background contradicts this, the article's professional layout and confident tone made her question the established consensus, illustrating how misinformation can target even educated individuals.</t>
+  </si>
+  <si>
+    <t>Robert follows several online forums where conspiracy theories are prevalent. He encountered a post claiming that a global elite controls world events. Despite the lack of credible evidence, the post resonated with his distrust of authority, leading him to adopt this worldview. This shows how misinformation can exploit existing anxieties.</t>
+  </si>
+  <si>
+    <t>Elena shared a social media post about a supposed cure for cancer. The post used scientific-sounding jargon and testimonials, making it seem legitimate. Later, she discovered it was a hoax. This experience highlights the persuasive power of misinformation disguised as scientific fact.</t>
+  </si>
+  <si>
+    <t>Kenji relies heavily on messaging apps for news. He received a forwarded message claiming a specific political candidate is corrupt. Without verifying the information, he shared it with his contacts, contributing to the spread of disinformation. This demonstrates the ease with which misinformation spreads through closed networks.</t>
+  </si>
+  <si>
+    <t>Fatima encountered a manipulated video clip of a politician making inflammatory remarks. Believing the video to be genuine, she became outraged. This illustrates the dangers of deepfakes and manipulated media in shaping public opinion.</t>
+  </si>
+  <si>
+    <t>Patrick listens to a radio show known for its nationalistic and xenophobic rhetoric. He heard a segment blaming immigrants for economic problems. This narrative resonated with his own economic anxieties, reinforcing his negative views on immigration.</t>
+  </si>
+  <si>
+    <t>Ingrid was targeted by online advertisements promoting a miracle weight loss product. The ads used before-and-after photos and testimonials, making the product seem credible. Despite her education, she purchased the product, only to find it ineffective. This demonstrates how targeted advertising can exploit vulnerabilities.</t>
+  </si>
+  <si>
+    <t>Javier works for a small news outlet that prioritizes speed over accuracy. He published an article based on unverified information from social media, which later turned out to be false. This case highlights the pressures faced by journalists in the fast-paced media landscape.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2230,7 +2865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2356,22 +2991,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2387,6 +3007,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2407,19 +3045,19 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="4" xr16:uid="{00000000-0016-0000-0000-000000000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="4" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="5" xr16:uid="{00000000-0016-0000-0100-000001000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="5" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="3" xr16:uid="{00000000-0016-0000-0200-000002000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="3" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="test_1" connectionId="2" xr16:uid="{00000000-0016-0000-0300-000003000000}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="test_1" connectionId="2" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2684,34 +3322,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:M106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:O106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="19.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="34.5703125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="18" customWidth="1"/>
-    <col min="13" max="13" width="3.5703125" style="18" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="3.140625" customWidth="1"/>
-    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="13.81640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.54296875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="19.453125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="34.54296875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="39" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="42.26953125" style="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="3.54296875" style="18" customWidth="1"/>
+    <col min="16" max="16" width="6.81640625" customWidth="1"/>
+    <col min="17" max="17" width="3.1796875" customWidth="1"/>
+    <col min="18" max="18" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.453125" customWidth="1"/>
+    <col min="20" max="20" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -2722,9 +3361,11 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:13" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -2753,15 +3394,21 @@
         <v>9</v>
       </c>
       <c r="K2" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="N2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="27"/>
-    </row>
-    <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="47">
+      <c r="O2" s="27"/>
+    </row>
+    <row r="3" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="53">
         <v>1</v>
       </c>
       <c r="C3" s="5">
@@ -2789,13 +3436,21 @@
         <v>15</v>
       </c>
       <c r="K3" s="28" t="s">
+        <v>559</v>
+      </c>
+      <c r="L3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="37"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="47"/>
+      <c r="M3" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="N3" s="30" t="s">
+        <v>547</v>
+      </c>
+      <c r="O3" s="37"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="53"/>
       <c r="C4" s="5">
         <v>2</v>
       </c>
@@ -2820,14 +3475,22 @@
       <c r="J4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="49" t="s">
+        <v>560</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="37"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="47"/>
+      <c r="M4" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N4" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O4" s="37"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B5" s="53"/>
       <c r="C5" s="5">
         <v>3</v>
       </c>
@@ -2852,14 +3515,22 @@
       <c r="J5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="49" t="s">
+        <v>561</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="37"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
+      <c r="M5" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O5" s="37"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="53"/>
       <c r="C6" s="5">
         <v>4</v>
       </c>
@@ -2884,14 +3555,22 @@
       <c r="J6" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="49" t="s">
+        <v>562</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="37"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
+      <c r="M6" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="O6" s="37"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="53"/>
       <c r="C7" s="21">
         <v>5</v>
       </c>
@@ -2917,13 +3596,21 @@
         <v>38</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="37"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="47"/>
+      <c r="M7" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="O7" s="37"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="53"/>
       <c r="C8" s="5">
         <v>6</v>
       </c>
@@ -2948,14 +3635,22 @@
       <c r="J8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="49" t="s">
+        <v>564</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="37"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
+      <c r="M8" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O8" s="37"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="53"/>
       <c r="C9" s="5">
         <v>7</v>
       </c>
@@ -2980,14 +3675,22 @@
       <c r="J9" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="49" t="s">
+        <v>565</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="37"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
+      <c r="M9" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O9" s="37"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="53"/>
       <c r="C10" s="5">
         <v>8</v>
       </c>
@@ -3012,14 +3715,22 @@
       <c r="J10" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="49" t="s">
+        <v>566</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="37"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="47"/>
+      <c r="M10" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="O10" s="37"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="53"/>
       <c r="C11" s="5">
         <v>9</v>
       </c>
@@ -3044,14 +3755,22 @@
       <c r="J11" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="49" t="s">
+        <v>567</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="8"/>
-      <c r="M11" s="37"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
+      <c r="M11" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="O11" s="37"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="54"/>
       <c r="C12" s="9">
         <v>10</v>
       </c>
@@ -3077,13 +3796,21 @@
         <v>65</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="37"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="49">
+      <c r="M12" s="49" t="s">
+        <v>554</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>554</v>
+      </c>
+      <c r="O12" s="37"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="55">
         <v>2</v>
       </c>
       <c r="C13" s="12">
@@ -3111,13 +3838,21 @@
         <v>69</v>
       </c>
       <c r="K13" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="37"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="47"/>
+      <c r="M13" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O13" s="37"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="53"/>
       <c r="C14" s="5">
         <v>2</v>
       </c>
@@ -3142,14 +3877,22 @@
       <c r="J14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="49" t="s">
+        <v>570</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="37"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
+      <c r="M14" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O14" s="37"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="53"/>
       <c r="C15" s="5">
         <v>3</v>
       </c>
@@ -3174,14 +3917,22 @@
       <c r="J15" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="49" t="s">
+        <v>571</v>
+      </c>
+      <c r="L15" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="37"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
+      <c r="M15" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O15" s="37"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="53"/>
       <c r="C16" s="5">
         <v>4</v>
       </c>
@@ -3206,14 +3957,22 @@
       <c r="J16" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="49" t="s">
+        <v>572</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="37"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" s="47"/>
+      <c r="M16" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="O16" s="37"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="53"/>
       <c r="C17" s="21">
         <v>5</v>
       </c>
@@ -3239,13 +3998,21 @@
         <v>80</v>
       </c>
       <c r="K17" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="37"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="47"/>
+      <c r="M17" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O17" s="37"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B18" s="53"/>
       <c r="C18" s="5">
         <v>6</v>
       </c>
@@ -3270,14 +4037,22 @@
       <c r="J18" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="49" t="s">
+        <v>574</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="37"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="47"/>
+      <c r="M18" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O18" s="37"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="53"/>
       <c r="C19" s="5">
         <v>7</v>
       </c>
@@ -3302,14 +4077,22 @@
       <c r="J19" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="49" t="s">
+        <v>575</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="37"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="47"/>
+      <c r="M19" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="O19" s="37"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="53"/>
       <c r="C20" s="5">
         <v>8</v>
       </c>
@@ -3334,14 +4117,22 @@
       <c r="J20" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="49" t="s">
+        <v>576</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="37"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="47"/>
+      <c r="M20" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="O20" s="37"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B21" s="53"/>
       <c r="C21" s="5">
         <v>9</v>
       </c>
@@ -3366,14 +4157,22 @@
       <c r="J21" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="49" t="s">
+        <v>577</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="L21" s="8"/>
-      <c r="M21" s="37"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="48"/>
+      <c r="M21" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="O21" s="37"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="54"/>
       <c r="C22" s="9">
         <v>10</v>
       </c>
@@ -3399,13 +4198,21 @@
         <v>96</v>
       </c>
       <c r="K22" s="10" t="s">
+        <v>578</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="37"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="49">
+      <c r="M22" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="O22" s="37"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B23" s="55">
         <v>3</v>
       </c>
       <c r="C23" s="12">
@@ -3433,13 +4240,21 @@
         <v>22</v>
       </c>
       <c r="K23" s="13" t="s">
+        <v>579</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="L23" s="8"/>
-      <c r="M23" s="37"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="47"/>
+      <c r="M23" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O23" s="37"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="53"/>
       <c r="C24" s="5">
         <v>2</v>
       </c>
@@ -3464,14 +4279,22 @@
       <c r="J24" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="49" t="s">
+        <v>580</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="37"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="47"/>
+      <c r="M24" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O24" s="37"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="53"/>
       <c r="C25" s="5">
         <v>3</v>
       </c>
@@ -3496,14 +4319,22 @@
       <c r="J25" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="49" t="s">
+        <v>581</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="37"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="47"/>
+      <c r="M25" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="O25" s="37"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="53"/>
       <c r="C26" s="5">
         <v>4</v>
       </c>
@@ -3528,14 +4359,22 @@
       <c r="J26" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="49" t="s">
+        <v>582</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="37"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="47"/>
+      <c r="M26" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="O26" s="37"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B27" s="53"/>
       <c r="C27" s="21">
         <v>5</v>
       </c>
@@ -3561,13 +4400,21 @@
         <v>111</v>
       </c>
       <c r="K27" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="L27" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="L27" s="8"/>
-      <c r="M27" s="37"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="47"/>
+      <c r="M27" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O27" s="37"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="53"/>
       <c r="C28" s="5">
         <v>6</v>
       </c>
@@ -3592,14 +4439,22 @@
       <c r="J28" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="49" t="s">
+        <v>584</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="L28" s="8"/>
-      <c r="M28" s="37"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="47"/>
+      <c r="M28" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="O28" s="37"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="53"/>
       <c r="C29" s="5">
         <v>7</v>
       </c>
@@ -3624,14 +4479,22 @@
       <c r="J29" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="49" t="s">
+        <v>585</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="37"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="47"/>
+      <c r="M29" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="O29" s="37"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B30" s="53"/>
       <c r="C30" s="5">
         <v>8</v>
       </c>
@@ -3656,14 +4519,22 @@
       <c r="J30" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="49" t="s">
+        <v>586</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="L30" s="8"/>
-      <c r="M30" s="37"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="47"/>
+      <c r="M30" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="O30" s="37"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="53"/>
       <c r="C31" s="5">
         <v>9</v>
       </c>
@@ -3688,14 +4559,22 @@
       <c r="J31" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="49" t="s">
+        <v>587</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="L31" s="8"/>
-      <c r="M31" s="37"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="48"/>
+      <c r="M31" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O31" s="37"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B32" s="54"/>
       <c r="C32" s="9">
         <v>10</v>
       </c>
@@ -3721,13 +4600,21 @@
         <v>126</v>
       </c>
       <c r="K32" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="L32" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="L32" s="8"/>
-      <c r="M32" s="37"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="49">
+      <c r="M32" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O32" s="37"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="55">
         <v>4</v>
       </c>
       <c r="C33" s="12">
@@ -3755,13 +4642,21 @@
         <v>129</v>
       </c>
       <c r="K33" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="L33" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="L33" s="8"/>
-      <c r="M33" s="37"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
+      <c r="M33" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O33" s="37"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="53"/>
       <c r="C34" s="5">
         <v>2</v>
       </c>
@@ -3786,14 +4681,22 @@
       <c r="J34" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="49" t="s">
+        <v>590</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="L34" s="8"/>
-      <c r="M34" s="37"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="47"/>
+      <c r="M34" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="O34" s="37"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="53"/>
       <c r="C35" s="5">
         <v>3</v>
       </c>
@@ -3818,14 +4721,22 @@
       <c r="J35" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="K35" s="49" t="s">
+        <v>591</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="L35" s="8"/>
-      <c r="M35" s="37"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
+      <c r="M35" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>550</v>
+      </c>
+      <c r="O35" s="37"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B36" s="53"/>
       <c r="C36" s="5">
         <v>4</v>
       </c>
@@ -3850,14 +4761,22 @@
       <c r="J36" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="49" t="s">
+        <v>592</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="L36" s="8"/>
-      <c r="M36" s="37"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="47"/>
+      <c r="M36" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N36" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O36" s="37"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="53"/>
       <c r="C37" s="21">
         <v>5</v>
       </c>
@@ -3883,13 +4802,21 @@
         <v>76</v>
       </c>
       <c r="K37" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="L37" s="8"/>
-      <c r="M37" s="37"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
+      <c r="M37" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="N37" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O37" s="37"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="53"/>
       <c r="C38" s="5">
         <v>6</v>
       </c>
@@ -3914,14 +4841,22 @@
       <c r="J38" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="49" t="s">
+        <v>594</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="37"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="47"/>
+      <c r="M38" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="N38" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="O38" s="37"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B39" s="53"/>
       <c r="C39" s="5">
         <v>7</v>
       </c>
@@ -3946,14 +4881,22 @@
       <c r="J39" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="49" t="s">
+        <v>595</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="37"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="47"/>
+      <c r="M39" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="N39" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="O39" s="37"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="53"/>
       <c r="C40" s="5">
         <v>8</v>
       </c>
@@ -3978,14 +4921,22 @@
       <c r="J40" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="49" t="s">
+        <v>596</v>
+      </c>
+      <c r="L40" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="L40" s="8"/>
-      <c r="M40" s="37"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="47"/>
+      <c r="M40" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N40" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O40" s="37"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="53"/>
       <c r="C41" s="5">
         <v>9</v>
       </c>
@@ -4010,14 +4961,22 @@
       <c r="J41" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="49" t="s">
+        <v>597</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="L41" s="8"/>
-      <c r="M41" s="37"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="48"/>
+      <c r="M41" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N41" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O41" s="37"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="54"/>
       <c r="C42" s="9">
         <v>10</v>
       </c>
@@ -4043,13 +5002,21 @@
         <v>158</v>
       </c>
       <c r="K42" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="L42" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="37"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="49">
+      <c r="M42" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="N42" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O42" s="37"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="55">
         <v>5</v>
       </c>
       <c r="C43" s="12">
@@ -4077,13 +5044,21 @@
         <v>161</v>
       </c>
       <c r="K43" s="13" t="s">
+        <v>599</v>
+      </c>
+      <c r="L43" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="L43" s="8"/>
-      <c r="M43" s="37"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="47"/>
+      <c r="M43" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N43" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O43" s="37"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="53"/>
       <c r="C44" s="5">
         <v>2</v>
       </c>
@@ -4108,14 +5083,22 @@
       <c r="J44" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="49" t="s">
+        <v>600</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="L44" s="8"/>
-      <c r="M44" s="37"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="47"/>
+      <c r="M44" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N44" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="O44" s="37"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B45" s="53"/>
       <c r="C45" s="5">
         <v>3</v>
       </c>
@@ -4140,14 +5123,22 @@
       <c r="J45" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="49" t="s">
+        <v>608</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="37"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="47"/>
+      <c r="M45" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N45" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O45" s="37"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B46" s="53"/>
       <c r="C46" s="5">
         <v>4</v>
       </c>
@@ -4172,14 +5163,22 @@
       <c r="J46" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="49" t="s">
+        <v>601</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="L46" s="8"/>
-      <c r="M46" s="37"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="47"/>
+      <c r="M46" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N46" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="O46" s="37"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B47" s="53"/>
       <c r="C47" s="21">
         <v>5</v>
       </c>
@@ -4205,13 +5204,21 @@
         <v>168</v>
       </c>
       <c r="K47" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="L47" s="8"/>
-      <c r="M47" s="37"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="47"/>
+      <c r="M47" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N47" s="8" t="s">
+        <v>555</v>
+      </c>
+      <c r="O47" s="37"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B48" s="53"/>
       <c r="C48" s="5">
         <v>6</v>
       </c>
@@ -4236,14 +5243,22 @@
       <c r="J48" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="49" t="s">
+        <v>603</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="L48" s="8"/>
-      <c r="M48" s="37"/>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B49" s="47"/>
+      <c r="M48" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N48" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O48" s="37"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B49" s="53"/>
       <c r="C49" s="5">
         <v>7</v>
       </c>
@@ -4268,14 +5283,22 @@
       <c r="J49" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="49" t="s">
+        <v>604</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="L49" s="8"/>
-      <c r="M49" s="37"/>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B50" s="47"/>
+      <c r="M49" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="N49" s="8" t="s">
+        <v>551</v>
+      </c>
+      <c r="O49" s="37"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B50" s="53"/>
       <c r="C50" s="5">
         <v>8</v>
       </c>
@@ -4300,14 +5323,22 @@
       <c r="J50" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="49" t="s">
+        <v>605</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="L50" s="8"/>
-      <c r="M50" s="37"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B51" s="47"/>
+      <c r="M50" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N50" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="O50" s="37"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B51" s="53"/>
       <c r="C51" s="5">
         <v>9</v>
       </c>
@@ -4332,14 +5363,22 @@
       <c r="J51" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="49" t="s">
+        <v>606</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="L51" s="8"/>
-      <c r="M51" s="37"/>
-    </row>
-    <row r="52" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="50"/>
+      <c r="M51" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="N51" s="8" t="s">
+        <v>548</v>
+      </c>
+      <c r="O51" s="37"/>
+    </row>
+    <row r="52" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="56"/>
       <c r="C52" s="5">
         <v>10</v>
       </c>
@@ -4365,469 +5404,477 @@
         <v>65</v>
       </c>
       <c r="K52" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="L52" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="L52" s="36"/>
-      <c r="M52" s="37"/>
-    </row>
-    <row r="53" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="N52" s="36" t="s">
+        <v>550</v>
+      </c>
+      <c r="O52" s="37"/>
+    </row>
+    <row r="53" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="20"/>
-      <c r="L53" s="17"/>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N53" s="17"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
       <c r="E57" s="19"/>
       <c r="F57" s="19"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
       <c r="E61" s="19"/>
       <c r="F61" s="19"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
       <c r="E63" s="19"/>
       <c r="F63" s="19"/>
     </row>
-    <row r="64" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-    </row>
-    <row r="65" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+    </row>
+    <row r="65" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-    </row>
-    <row r="66" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+    </row>
+    <row r="66" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-    </row>
-    <row r="67" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+    </row>
+    <row r="67" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-    </row>
-    <row r="68" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+    </row>
+    <row r="68" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-    </row>
-    <row r="69" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+    </row>
+    <row r="69" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="19"/>
       <c r="F69" s="19"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-    </row>
-    <row r="70" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+    </row>
+    <row r="70" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
       <c r="E70" s="19"/>
       <c r="F70" s="19"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-    </row>
-    <row r="71" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+    </row>
+    <row r="71" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="19"/>
       <c r="F71" s="19"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-    </row>
-    <row r="72" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+    </row>
+    <row r="72" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
       <c r="E72" s="19"/>
       <c r="F72" s="19"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-    </row>
-    <row r="73" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+    </row>
+    <row r="73" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-    </row>
-    <row r="74" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+    </row>
+    <row r="74" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
       <c r="F74" s="19"/>
-      <c r="L74" s="18"/>
-      <c r="M74" s="18"/>
-    </row>
-    <row r="75" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+    </row>
+    <row r="75" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="19"/>
       <c r="F75" s="19"/>
-      <c r="L75" s="18"/>
-      <c r="M75" s="18"/>
-    </row>
-    <row r="76" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+    </row>
+    <row r="76" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
-      <c r="L76" s="18"/>
-      <c r="M76" s="18"/>
-    </row>
-    <row r="77" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+    </row>
+    <row r="77" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="19"/>
       <c r="F77" s="19"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
-    </row>
-    <row r="78" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+    </row>
+    <row r="78" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
       <c r="E78" s="19"/>
       <c r="F78" s="19"/>
-      <c r="L78" s="18"/>
-      <c r="M78" s="18"/>
-    </row>
-    <row r="79" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
+    </row>
+    <row r="79" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
       <c r="E79" s="19"/>
       <c r="F79" s="19"/>
-      <c r="L79" s="18"/>
-      <c r="M79" s="18"/>
-    </row>
-    <row r="80" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N79" s="18"/>
+      <c r="O79" s="18"/>
+    </row>
+    <row r="80" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="19"/>
       <c r="F80" s="19"/>
-      <c r="L80" s="18"/>
-      <c r="M80" s="18"/>
-    </row>
-    <row r="81" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
+    </row>
+    <row r="81" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
       <c r="E81" s="19"/>
       <c r="F81" s="19"/>
-      <c r="L81" s="18"/>
-      <c r="M81" s="18"/>
-    </row>
-    <row r="82" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+    </row>
+    <row r="82" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
       <c r="E82" s="19"/>
       <c r="F82" s="19"/>
-      <c r="L82" s="18"/>
-      <c r="M82" s="18"/>
-    </row>
-    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+    </row>
+    <row r="83" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="19"/>
       <c r="F83" s="19"/>
-      <c r="L83" s="18"/>
-      <c r="M83" s="18"/>
-    </row>
-    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+    </row>
+    <row r="84" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
-      <c r="L84" s="18"/>
-      <c r="M84" s="18"/>
-    </row>
-    <row r="85" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
+    </row>
+    <row r="85" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
       <c r="E85" s="19"/>
       <c r="F85" s="19"/>
-      <c r="L85" s="18"/>
-      <c r="M85" s="18"/>
-    </row>
-    <row r="86" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
+    </row>
+    <row r="86" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
       <c r="E86" s="19"/>
       <c r="F86" s="19"/>
-      <c r="L86" s="18"/>
-      <c r="M86" s="18"/>
-    </row>
-    <row r="87" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
+    </row>
+    <row r="87" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
-      <c r="L87" s="18"/>
-      <c r="M87" s="18"/>
-    </row>
-    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
+    </row>
+    <row r="88" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
-      <c r="L88" s="18"/>
-      <c r="M88" s="18"/>
-    </row>
-    <row r="89" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+    </row>
+    <row r="89" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
       <c r="E89" s="19"/>
       <c r="F89" s="19"/>
-      <c r="L89" s="18"/>
-      <c r="M89" s="18"/>
-    </row>
-    <row r="90" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+    </row>
+    <row r="90" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
       <c r="E90" s="19"/>
       <c r="F90" s="19"/>
-      <c r="L90" s="18"/>
-      <c r="M90" s="18"/>
-    </row>
-    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N90" s="18"/>
+      <c r="O90" s="18"/>
+    </row>
+    <row r="91" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
-      <c r="L91" s="18"/>
-      <c r="M91" s="18"/>
-    </row>
-    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
+    </row>
+    <row r="92" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
       <c r="E92" s="19"/>
       <c r="F92" s="19"/>
-      <c r="L92" s="18"/>
-      <c r="M92" s="18"/>
-    </row>
-    <row r="93" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
+    </row>
+    <row r="93" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
       <c r="E93" s="19"/>
       <c r="F93" s="19"/>
-      <c r="L93" s="18"/>
-      <c r="M93" s="18"/>
-    </row>
-    <row r="94" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="18"/>
+      <c r="O93" s="18"/>
+    </row>
+    <row r="94" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
       <c r="E94" s="19"/>
       <c r="F94" s="19"/>
-      <c r="L94" s="18"/>
-      <c r="M94" s="18"/>
-    </row>
-    <row r="95" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N94" s="18"/>
+      <c r="O94" s="18"/>
+    </row>
+    <row r="95" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="19"/>
       <c r="F95" s="19"/>
-      <c r="L95" s="18"/>
-      <c r="M95" s="18"/>
-    </row>
-    <row r="96" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N95" s="18"/>
+      <c r="O95" s="18"/>
+    </row>
+    <row r="96" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
-      <c r="L96" s="18"/>
-      <c r="M96" s="18"/>
-    </row>
-    <row r="97" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N96" s="18"/>
+      <c r="O96" s="18"/>
+    </row>
+    <row r="97" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
-      <c r="L97" s="18"/>
-      <c r="M97" s="18"/>
-    </row>
-    <row r="98" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="18"/>
+      <c r="O97" s="18"/>
+    </row>
+    <row r="98" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
       <c r="E98" s="19"/>
       <c r="F98" s="19"/>
-      <c r="L98" s="18"/>
-      <c r="M98" s="18"/>
-    </row>
-    <row r="99" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N98" s="18"/>
+      <c r="O98" s="18"/>
+    </row>
+    <row r="99" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
       <c r="E99" s="19"/>
       <c r="F99" s="19"/>
-      <c r="L99" s="18"/>
-      <c r="M99" s="18"/>
-    </row>
-    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N99" s="18"/>
+      <c r="O99" s="18"/>
+    </row>
+    <row r="100" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="19"/>
       <c r="F100" s="19"/>
-      <c r="L100" s="18"/>
-      <c r="M100" s="18"/>
-    </row>
-    <row r="101" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N100" s="18"/>
+      <c r="O100" s="18"/>
+    </row>
+    <row r="101" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="L101" s="18"/>
-      <c r="M101" s="18"/>
-    </row>
-    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N101" s="18"/>
+      <c r="O101" s="18"/>
+    </row>
+    <row r="102" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="19"/>
       <c r="F102" s="19"/>
-      <c r="L102" s="18"/>
-      <c r="M102" s="18"/>
-    </row>
-    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="18"/>
+      <c r="O102" s="18"/>
+    </row>
+    <row r="103" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
-      <c r="L103" s="18"/>
-      <c r="M103" s="18"/>
-    </row>
-    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N103" s="18"/>
+      <c r="O103" s="18"/>
+    </row>
+    <row r="104" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
-      <c r="L104" s="18"/>
-      <c r="M104" s="18"/>
-    </row>
-    <row r="105" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N104" s="18"/>
+      <c r="O104" s="18"/>
+    </row>
+    <row r="105" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
       <c r="D105" s="19"/>
       <c r="E105" s="19"/>
       <c r="F105" s="19"/>
-      <c r="L105" s="18"/>
-      <c r="M105" s="18"/>
-    </row>
-    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N105" s="18"/>
+      <c r="O105" s="18"/>
+    </row>
+    <row r="106" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
       <c r="D106" s="19"/>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
-      <c r="L106" s="18"/>
-      <c r="M106" s="18"/>
+      <c r="N106" s="18"/>
+      <c r="O106" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4843,33 +5890,34 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:L106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:N106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38.85546875" style="3" customWidth="1"/>
-    <col min="12" max="12" width="44.28515625" style="18" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="20.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.453125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.54296875" style="3" customWidth="1"/>
+    <col min="12" max="13" width="38.81640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="44.26953125" style="18" customWidth="1"/>
+    <col min="15" max="15" width="6.81640625" customWidth="1"/>
+    <col min="16" max="16" width="3.1796875" customWidth="1"/>
+    <col min="17" max="17" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" customWidth="1"/>
+    <col min="19" max="19" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -4880,9 +5928,11 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -4911,14 +5961,20 @@
         <v>9</v>
       </c>
       <c r="K2" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="N2" s="26" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="47">
+    <row r="3" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="53">
         <v>1</v>
       </c>
       <c r="C3" s="5">
@@ -4945,13 +6001,18 @@
       <c r="J3" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="29" t="s">
+        <v>609</v>
+      </c>
+      <c r="L3" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="L3" s="43"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="47"/>
+      <c r="M3" s="50" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B4" s="53"/>
       <c r="C4" s="5">
         <v>2</v>
       </c>
@@ -4976,13 +6037,18 @@
       <c r="J4" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="K4" s="39" t="s">
+      <c r="K4" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="L4" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="L4" s="44"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="47"/>
+      <c r="M4" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B5" s="53"/>
       <c r="C5" s="5">
         <v>3</v>
       </c>
@@ -5007,13 +6073,18 @@
       <c r="J5" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="L5" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="L5" s="44"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
+      <c r="M5" s="51" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B6" s="53"/>
       <c r="C6" s="5">
         <v>4</v>
       </c>
@@ -5038,13 +6109,18 @@
       <c r="J6" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="K6" s="39" t="s">
+      <c r="K6" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="L6" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="L6" s="44"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
+      <c r="M6" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B7" s="53"/>
       <c r="C7" s="21">
         <v>5</v>
       </c>
@@ -5069,13 +6145,18 @@
       <c r="J7" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="K7" s="39" t="s">
+      <c r="K7" s="7" t="s">
+        <v>613</v>
+      </c>
+      <c r="L7" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="L7" s="44"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="47"/>
+      <c r="M7" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B8" s="53"/>
       <c r="C8" s="5">
         <v>6</v>
       </c>
@@ -5100,13 +6181,18 @@
       <c r="J8" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="K8" s="39" t="s">
+      <c r="K8" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="L8" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="L8" s="44"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
+      <c r="M8" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B9" s="53"/>
       <c r="C9" s="5">
         <v>7</v>
       </c>
@@ -5131,13 +6217,18 @@
       <c r="J9" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="L9" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="L9" s="44"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
+      <c r="M9" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B10" s="53"/>
       <c r="C10" s="5">
         <v>8</v>
       </c>
@@ -5162,13 +6253,18 @@
       <c r="J10" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="K10" s="39" t="s">
+      <c r="K10" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="L10" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="L10" s="44"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="47"/>
+      <c r="M10" s="51" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B11" s="53"/>
       <c r="C11" s="5">
         <v>9</v>
       </c>
@@ -5193,13 +6289,18 @@
       <c r="J11" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="K11" s="39" t="s">
+      <c r="K11" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="L11" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="L11" s="44"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
+      <c r="M11" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B12" s="54"/>
       <c r="C12" s="9">
         <v>10</v>
       </c>
@@ -5224,13 +6325,18 @@
       <c r="J12" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K12" s="11" t="s">
+        <v>618</v>
+      </c>
+      <c r="L12" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="L12" s="44"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="49">
+      <c r="M12" s="51" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B13" s="55">
         <v>2</v>
       </c>
       <c r="C13" s="12">
@@ -5257,13 +6363,18 @@
       <c r="J13" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="41" t="s">
+      <c r="K13" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="L13" s="41" t="s">
         <v>216</v>
       </c>
-      <c r="L13" s="44"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="47"/>
+      <c r="M13" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B14" s="53"/>
       <c r="C14" s="5">
         <v>2</v>
       </c>
@@ -5288,13 +6399,18 @@
       <c r="J14" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="39" t="s">
+      <c r="K14" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="L14" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="L14" s="44"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
+      <c r="M14" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B15" s="53"/>
       <c r="C15" s="5">
         <v>3</v>
       </c>
@@ -5319,13 +6435,18 @@
       <c r="J15" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="K15" s="39" t="s">
+      <c r="K15" s="7" t="s">
+        <v>621</v>
+      </c>
+      <c r="L15" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="L15" s="44"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
+      <c r="M15" s="51" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B16" s="53"/>
       <c r="C16" s="5">
         <v>4</v>
       </c>
@@ -5350,13 +6471,18 @@
       <c r="J16" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="K16" s="39" t="s">
+      <c r="K16" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="L16" s="39" t="s">
         <v>225</v>
       </c>
-      <c r="L16" s="44"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="47"/>
+      <c r="M16" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B17" s="53"/>
       <c r="C17" s="21">
         <v>5</v>
       </c>
@@ -5381,13 +6507,18 @@
       <c r="J17" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="K17" s="39" t="s">
+      <c r="K17" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="L17" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="L17" s="44"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="47"/>
+      <c r="M17" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B18" s="53"/>
       <c r="C18" s="5">
         <v>6</v>
       </c>
@@ -5412,13 +6543,18 @@
       <c r="J18" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="K18" s="39" t="s">
+      <c r="K18" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="L18" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="L18" s="44"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="47"/>
+      <c r="M18" s="51" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B19" s="53"/>
       <c r="C19" s="5">
         <v>7</v>
       </c>
@@ -5443,13 +6579,18 @@
       <c r="J19" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="K19" s="39" t="s">
+      <c r="K19" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="L19" s="39" t="s">
         <v>237</v>
       </c>
-      <c r="L19" s="44"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="47"/>
+      <c r="M19" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B20" s="53"/>
       <c r="C20" s="5">
         <v>8</v>
       </c>
@@ -5474,13 +6615,18 @@
       <c r="J20" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="K20" s="39" t="s">
+      <c r="K20" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="L20" s="39" t="s">
         <v>241</v>
       </c>
-      <c r="L20" s="44"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="47"/>
+      <c r="M20" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B21" s="53"/>
       <c r="C21" s="5">
         <v>9</v>
       </c>
@@ -5505,13 +6651,18 @@
       <c r="J21" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K21" s="39" t="s">
+      <c r="K21" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="L21" s="39" t="s">
         <v>243</v>
       </c>
-      <c r="L21" s="44"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="48"/>
+      <c r="M21" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B22" s="54"/>
       <c r="C22" s="9">
         <v>10</v>
       </c>
@@ -5536,13 +6687,18 @@
       <c r="J22" s="11" t="s">
         <v>246</v>
       </c>
-      <c r="K22" s="40" t="s">
+      <c r="K22" s="11" t="s">
+        <v>628</v>
+      </c>
+      <c r="L22" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="L22" s="44"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="49">
+      <c r="M22" s="51" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B23" s="55">
         <v>3</v>
       </c>
       <c r="C23" s="12">
@@ -5569,13 +6725,18 @@
       <c r="J23" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="K23" s="41" t="s">
+      <c r="K23" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="L23" s="41" t="s">
         <v>250</v>
       </c>
-      <c r="L23" s="44"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="47"/>
+      <c r="M23" s="51" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B24" s="53"/>
       <c r="C24" s="5">
         <v>2</v>
       </c>
@@ -5600,13 +6761,18 @@
       <c r="J24" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="K24" s="39" t="s">
+      <c r="K24" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="L24" s="39" t="s">
         <v>254</v>
       </c>
-      <c r="L24" s="44"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="47"/>
+      <c r="M24" s="51" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B25" s="53"/>
       <c r="C25" s="5">
         <v>3</v>
       </c>
@@ -5631,13 +6797,18 @@
       <c r="J25" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="K25" s="39" t="s">
+      <c r="K25" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="L25" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="L25" s="44"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="47"/>
+      <c r="M25" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B26" s="53"/>
       <c r="C26" s="5">
         <v>4</v>
       </c>
@@ -5662,13 +6833,18 @@
       <c r="J26" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="K26" s="39" t="s">
+      <c r="K26" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="L26" s="39" t="s">
         <v>261</v>
       </c>
-      <c r="L26" s="44"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="47"/>
+      <c r="M26" s="51" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B27" s="53"/>
       <c r="C27" s="21">
         <v>5</v>
       </c>
@@ -5693,13 +6869,18 @@
       <c r="J27" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="K27" s="39" t="s">
+      <c r="K27" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="L27" s="39" t="s">
         <v>265</v>
       </c>
-      <c r="L27" s="44"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="47"/>
+      <c r="M27" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B28" s="53"/>
       <c r="C28" s="5">
         <v>6</v>
       </c>
@@ -5724,13 +6905,18 @@
       <c r="J28" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="K28" s="39" t="s">
+      <c r="K28" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="L28" s="39" t="s">
         <v>269</v>
       </c>
-      <c r="L28" s="44"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="47"/>
+      <c r="M28" s="51" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B29" s="53"/>
       <c r="C29" s="5">
         <v>7</v>
       </c>
@@ -5755,13 +6941,18 @@
       <c r="J29" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="K29" s="39" t="s">
+      <c r="K29" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="L29" s="39" t="s">
         <v>272</v>
       </c>
-      <c r="L29" s="44"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="47"/>
+      <c r="M29" s="51" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B30" s="53"/>
       <c r="C30" s="5">
         <v>8</v>
       </c>
@@ -5786,13 +6977,18 @@
       <c r="J30" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="K30" s="39" t="s">
+      <c r="K30" s="7" t="s">
+        <v>636</v>
+      </c>
+      <c r="L30" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="L30" s="44"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="47"/>
+      <c r="M30" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B31" s="53"/>
       <c r="C31" s="5">
         <v>9</v>
       </c>
@@ -5817,13 +7013,18 @@
       <c r="J31" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="K31" s="39" t="s">
+      <c r="K31" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="L31" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="L31" s="44"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="48"/>
+      <c r="M31" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B32" s="54"/>
       <c r="C32" s="9">
         <v>10</v>
       </c>
@@ -5848,13 +7049,18 @@
       <c r="J32" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="K32" s="40" t="s">
+      <c r="K32" s="11" t="s">
+        <v>638</v>
+      </c>
+      <c r="L32" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="L32" s="44"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="49">
+      <c r="M32" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B33" s="55">
         <v>4</v>
       </c>
       <c r="C33" s="12">
@@ -5881,13 +7087,18 @@
       <c r="J33" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="K33" s="41" t="s">
+      <c r="K33" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="L33" s="41" t="s">
         <v>165</v>
       </c>
-      <c r="L33" s="44"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
+      <c r="M33" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B34" s="53"/>
       <c r="C34" s="5">
         <v>2</v>
       </c>
@@ -5912,13 +7123,18 @@
       <c r="J34" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="K34" s="39" t="s">
+      <c r="K34" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="L34" s="39" t="s">
         <v>216</v>
       </c>
-      <c r="L34" s="44"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B35" s="47"/>
+      <c r="M34" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B35" s="53"/>
       <c r="C35" s="5">
         <v>3</v>
       </c>
@@ -5943,13 +7159,18 @@
       <c r="J35" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="K35" s="39" t="s">
+      <c r="K35" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="L35" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="L35" s="44"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
+      <c r="M35" s="51" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B36" s="53"/>
       <c r="C36" s="5">
         <v>4</v>
       </c>
@@ -5974,13 +7195,18 @@
       <c r="J36" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="K36" s="39" t="s">
+      <c r="K36" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="L36" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="L36" s="44"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="47"/>
+      <c r="M36" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B37" s="53"/>
       <c r="C37" s="21">
         <v>5</v>
       </c>
@@ -6005,13 +7231,18 @@
       <c r="J37" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="K37" s="39" t="s">
+      <c r="K37" s="7" t="s">
+        <v>643</v>
+      </c>
+      <c r="L37" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="L37" s="44"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
+      <c r="M37" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B38" s="53"/>
       <c r="C38" s="5">
         <v>6</v>
       </c>
@@ -6036,13 +7267,18 @@
       <c r="J38" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K38" s="39" t="s">
+      <c r="K38" s="7" t="s">
+        <v>644</v>
+      </c>
+      <c r="L38" s="39" t="s">
         <v>303</v>
       </c>
-      <c r="L38" s="44"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" s="47"/>
+      <c r="M38" s="51" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B39" s="53"/>
       <c r="C39" s="5">
         <v>7</v>
       </c>
@@ -6067,13 +7303,18 @@
       <c r="J39" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="K39" s="39" t="s">
+      <c r="K39" s="7" t="s">
+        <v>645</v>
+      </c>
+      <c r="L39" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="L39" s="44"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" s="47"/>
+      <c r="M39" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B40" s="53"/>
       <c r="C40" s="5">
         <v>8</v>
       </c>
@@ -6098,13 +7339,18 @@
       <c r="J40" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K40" s="39" t="s">
+      <c r="K40" s="7" t="s">
+        <v>646</v>
+      </c>
+      <c r="L40" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="L40" s="44"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="47"/>
+      <c r="M40" s="51" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B41" s="53"/>
       <c r="C41" s="5">
         <v>9</v>
       </c>
@@ -6129,13 +7375,18 @@
       <c r="J41" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="K41" s="39" t="s">
+      <c r="K41" s="7" t="s">
+        <v>647</v>
+      </c>
+      <c r="L41" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="L41" s="44"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="48"/>
+      <c r="M41" s="51" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B42" s="54"/>
       <c r="C42" s="9">
         <v>10</v>
       </c>
@@ -6160,13 +7411,18 @@
       <c r="J42" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="K42" s="40" t="s">
+      <c r="K42" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="L42" s="40" t="s">
         <v>320</v>
       </c>
-      <c r="L42" s="44"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="49">
+      <c r="M42" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B43" s="55">
         <v>5</v>
       </c>
       <c r="C43" s="12">
@@ -6193,13 +7449,18 @@
       <c r="J43" s="14" t="s">
         <v>321</v>
       </c>
-      <c r="K43" s="41" t="s">
+      <c r="K43" s="14" t="s">
+        <v>649</v>
+      </c>
+      <c r="L43" s="41" t="s">
         <v>185</v>
       </c>
-      <c r="L43" s="44"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B44" s="47"/>
+      <c r="M43" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B44" s="53"/>
       <c r="C44" s="5">
         <v>2</v>
       </c>
@@ -6224,13 +7485,18 @@
       <c r="J44" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="K44" s="39" t="s">
+      <c r="K44" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="L44" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="L44" s="44"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B45" s="47"/>
+      <c r="M44" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B45" s="53"/>
       <c r="C45" s="5">
         <v>3</v>
       </c>
@@ -6255,13 +7521,18 @@
       <c r="J45" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="K45" s="39" t="s">
+      <c r="K45" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="L45" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="L45" s="44"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="47"/>
+      <c r="M45" s="51" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B46" s="53"/>
       <c r="C46" s="5">
         <v>4</v>
       </c>
@@ -6286,13 +7557,18 @@
       <c r="J46" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K46" s="39" t="s">
+      <c r="K46" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="L46" s="39" t="s">
         <v>328</v>
       </c>
-      <c r="L46" s="44"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47" s="47"/>
+      <c r="M46" s="51" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B47" s="53"/>
       <c r="C47" s="21">
         <v>5</v>
       </c>
@@ -6317,13 +7593,18 @@
       <c r="J47" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="K47" s="39" t="s">
+      <c r="K47" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="L47" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="L47" s="44"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B48" s="47"/>
+      <c r="M47" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.35">
+      <c r="B48" s="53"/>
       <c r="C48" s="5">
         <v>6</v>
       </c>
@@ -6348,13 +7629,18 @@
       <c r="J48" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="K48" s="39" t="s">
+      <c r="K48" s="7" t="s">
+        <v>654</v>
+      </c>
+      <c r="L48" s="39" t="s">
         <v>333</v>
       </c>
-      <c r="L48" s="44"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B49" s="47"/>
+      <c r="M48" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B49" s="53"/>
       <c r="C49" s="5">
         <v>7</v>
       </c>
@@ -6379,13 +7665,18 @@
       <c r="J49" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="K49" s="39" t="s">
+      <c r="K49" s="7" t="s">
+        <v>655</v>
+      </c>
+      <c r="L49" s="39" t="s">
         <v>335</v>
       </c>
-      <c r="L49" s="44"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B50" s="47"/>
+      <c r="M49" s="51" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B50" s="53"/>
       <c r="C50" s="5">
         <v>8</v>
       </c>
@@ -6410,13 +7701,18 @@
       <c r="J50" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="K50" s="39" t="s">
+      <c r="K50" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="L50" s="39" t="s">
         <v>339</v>
       </c>
-      <c r="L50" s="44"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B51" s="47"/>
+      <c r="M50" s="51" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B51" s="53"/>
       <c r="C51" s="5">
         <v>9</v>
       </c>
@@ -6441,13 +7737,18 @@
       <c r="J51" s="7" t="s">
         <v>343</v>
       </c>
-      <c r="K51" s="39" t="s">
+      <c r="K51" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="L51" s="39" t="s">
         <v>344</v>
       </c>
-      <c r="L51" s="44"/>
-    </row>
-    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="50"/>
+      <c r="M51" s="51" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="52" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="56"/>
       <c r="C52" s="5">
         <v>10</v>
       </c>
@@ -6472,426 +7773,431 @@
       <c r="J52" s="16" t="s">
         <v>347</v>
       </c>
-      <c r="K52" s="42" t="s">
+      <c r="K52" s="16" t="s">
+        <v>658</v>
+      </c>
+      <c r="L52" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="L52" s="45"/>
-    </row>
-    <row r="53" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="52" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="53" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="20"/>
-      <c r="L53" s="17"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="N53" s="17"/>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
       <c r="E57" s="19"/>
       <c r="F57" s="19"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
       <c r="E61" s="19"/>
       <c r="F61" s="19"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
       <c r="E63" s="19"/>
       <c r="F63" s="19"/>
     </row>
-    <row r="64" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
-      <c r="L64" s="18"/>
-    </row>
-    <row r="65" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N64" s="18"/>
+    </row>
+    <row r="65" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
-      <c r="L65" s="18"/>
-    </row>
-    <row r="66" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N65" s="18"/>
+    </row>
+    <row r="66" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
-      <c r="L66" s="18"/>
-    </row>
-    <row r="67" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N66" s="18"/>
+    </row>
+    <row r="67" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
-      <c r="L67" s="18"/>
-    </row>
-    <row r="68" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="18"/>
+    </row>
+    <row r="68" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
-      <c r="L68" s="18"/>
-    </row>
-    <row r="69" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N68" s="18"/>
+    </row>
+    <row r="69" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="19"/>
       <c r="F69" s="19"/>
-      <c r="L69" s="18"/>
-    </row>
-    <row r="70" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N69" s="18"/>
+    </row>
+    <row r="70" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
       <c r="E70" s="19"/>
       <c r="F70" s="19"/>
-      <c r="L70" s="18"/>
-    </row>
-    <row r="71" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N70" s="18"/>
+    </row>
+    <row r="71" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="19"/>
       <c r="F71" s="19"/>
-      <c r="L71" s="18"/>
-    </row>
-    <row r="72" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N71" s="18"/>
+    </row>
+    <row r="72" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
       <c r="E72" s="19"/>
       <c r="F72" s="19"/>
-      <c r="L72" s="18"/>
-    </row>
-    <row r="73" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N72" s="18"/>
+    </row>
+    <row r="73" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
-      <c r="L73" s="18"/>
-    </row>
-    <row r="74" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N73" s="18"/>
+    </row>
+    <row r="74" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
       <c r="F74" s="19"/>
-      <c r="L74" s="18"/>
-    </row>
-    <row r="75" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N74" s="18"/>
+    </row>
+    <row r="75" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="19"/>
       <c r="F75" s="19"/>
-      <c r="L75" s="18"/>
-    </row>
-    <row r="76" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N75" s="18"/>
+    </row>
+    <row r="76" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
-      <c r="L76" s="18"/>
-    </row>
-    <row r="77" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N76" s="18"/>
+    </row>
+    <row r="77" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="19"/>
       <c r="F77" s="19"/>
-      <c r="L77" s="18"/>
-    </row>
-    <row r="78" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="18"/>
+    </row>
+    <row r="78" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
       <c r="E78" s="19"/>
       <c r="F78" s="19"/>
-      <c r="L78" s="18"/>
-    </row>
-    <row r="79" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N78" s="18"/>
+    </row>
+    <row r="79" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
       <c r="E79" s="19"/>
       <c r="F79" s="19"/>
-      <c r="L79" s="18"/>
-    </row>
-    <row r="80" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N79" s="18"/>
+    </row>
+    <row r="80" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="19"/>
       <c r="F80" s="19"/>
-      <c r="L80" s="18"/>
-    </row>
-    <row r="81" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N80" s="18"/>
+    </row>
+    <row r="81" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
       <c r="E81" s="19"/>
       <c r="F81" s="19"/>
-      <c r="L81" s="18"/>
-    </row>
-    <row r="82" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N81" s="18"/>
+    </row>
+    <row r="82" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
       <c r="E82" s="19"/>
       <c r="F82" s="19"/>
-      <c r="L82" s="18"/>
-    </row>
-    <row r="83" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N82" s="18"/>
+    </row>
+    <row r="83" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="19"/>
       <c r="F83" s="19"/>
-      <c r="L83" s="18"/>
-    </row>
-    <row r="84" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N83" s="18"/>
+    </row>
+    <row r="84" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
-      <c r="L84" s="18"/>
-    </row>
-    <row r="85" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N84" s="18"/>
+    </row>
+    <row r="85" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
       <c r="E85" s="19"/>
       <c r="F85" s="19"/>
-      <c r="L85" s="18"/>
-    </row>
-    <row r="86" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N85" s="18"/>
+    </row>
+    <row r="86" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
       <c r="E86" s="19"/>
       <c r="F86" s="19"/>
-      <c r="L86" s="18"/>
-    </row>
-    <row r="87" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N86" s="18"/>
+    </row>
+    <row r="87" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
-      <c r="L87" s="18"/>
-    </row>
-    <row r="88" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N87" s="18"/>
+    </row>
+    <row r="88" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
-      <c r="L88" s="18"/>
-    </row>
-    <row r="89" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N88" s="18"/>
+    </row>
+    <row r="89" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
       <c r="E89" s="19"/>
       <c r="F89" s="19"/>
-      <c r="L89" s="18"/>
-    </row>
-    <row r="90" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N89" s="18"/>
+    </row>
+    <row r="90" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
       <c r="E90" s="19"/>
       <c r="F90" s="19"/>
-      <c r="L90" s="18"/>
-    </row>
-    <row r="91" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N90" s="18"/>
+    </row>
+    <row r="91" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
-      <c r="L91" s="18"/>
-    </row>
-    <row r="92" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N91" s="18"/>
+    </row>
+    <row r="92" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
       <c r="E92" s="19"/>
       <c r="F92" s="19"/>
-      <c r="L92" s="18"/>
-    </row>
-    <row r="93" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="18"/>
+    </row>
+    <row r="93" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
       <c r="E93" s="19"/>
       <c r="F93" s="19"/>
-      <c r="L93" s="18"/>
-    </row>
-    <row r="94" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="18"/>
+    </row>
+    <row r="94" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
       <c r="E94" s="19"/>
       <c r="F94" s="19"/>
-      <c r="L94" s="18"/>
-    </row>
-    <row r="95" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N94" s="18"/>
+    </row>
+    <row r="95" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="19"/>
       <c r="F95" s="19"/>
-      <c r="L95" s="18"/>
-    </row>
-    <row r="96" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N95" s="18"/>
+    </row>
+    <row r="96" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
-      <c r="L96" s="18"/>
-    </row>
-    <row r="97" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N96" s="18"/>
+    </row>
+    <row r="97" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
-      <c r="L97" s="18"/>
-    </row>
-    <row r="98" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="18"/>
+    </row>
+    <row r="98" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
       <c r="E98" s="19"/>
       <c r="F98" s="19"/>
-      <c r="L98" s="18"/>
-    </row>
-    <row r="99" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N98" s="18"/>
+    </row>
+    <row r="99" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
       <c r="E99" s="19"/>
       <c r="F99" s="19"/>
-      <c r="L99" s="18"/>
-    </row>
-    <row r="100" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N99" s="18"/>
+    </row>
+    <row r="100" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="19"/>
       <c r="F100" s="19"/>
-      <c r="L100" s="18"/>
-    </row>
-    <row r="101" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N100" s="18"/>
+    </row>
+    <row r="101" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="L101" s="18"/>
-    </row>
-    <row r="102" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N101" s="18"/>
+    </row>
+    <row r="102" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="19"/>
       <c r="F102" s="19"/>
-      <c r="L102" s="18"/>
-    </row>
-    <row r="103" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="18"/>
+    </row>
+    <row r="103" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
-      <c r="L103" s="18"/>
-    </row>
-    <row r="104" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N103" s="18"/>
+    </row>
+    <row r="104" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
-      <c r="L104" s="18"/>
-    </row>
-    <row r="105" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N104" s="18"/>
+    </row>
+    <row r="105" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
       <c r="D105" s="19"/>
       <c r="E105" s="19"/>
       <c r="F105" s="19"/>
-      <c r="L105" s="18"/>
-    </row>
-    <row r="106" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N105" s="18"/>
+    </row>
+    <row r="106" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
       <c r="D106" s="19"/>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
-      <c r="L106" s="18"/>
+      <c r="N106" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6907,34 +8213,35 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:M106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:O106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="2.85546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="16.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="18.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="46.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5703125" style="18" customWidth="1"/>
-    <col min="13" max="13" width="12.42578125" style="18" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" customWidth="1"/>
-    <col min="15" max="15" width="3.140625" customWidth="1"/>
-    <col min="16" max="16" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.42578125" customWidth="1"/>
-    <col min="18" max="18" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="2" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7265625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="2.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.1796875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="16.54296875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="18.453125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="46.26953125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="46.26953125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="18.54296875" style="18" customWidth="1"/>
+    <col min="15" max="15" width="12.453125" style="18" customWidth="1"/>
+    <col min="16" max="16" width="6.81640625" customWidth="1"/>
+    <col min="17" max="17" width="3.1796875" customWidth="1"/>
+    <col min="18" max="18" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.453125" customWidth="1"/>
+    <col min="20" max="20" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -6945,9 +8252,11 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:13" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="2:15" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -6976,15 +8285,21 @@
         <v>9</v>
       </c>
       <c r="K2" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="N2" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="46"/>
-    </row>
-    <row r="3" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="47">
+      <c r="O2" s="43"/>
+    </row>
+    <row r="3" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="53">
         <v>1</v>
       </c>
       <c r="C3" s="5">
@@ -7012,13 +8327,19 @@
         <v>103</v>
       </c>
       <c r="K3" s="28" t="s">
+        <v>659</v>
+      </c>
+      <c r="L3" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="L3" s="30"/>
-      <c r="M3" s="37"/>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B4" s="47"/>
+      <c r="M3" s="28" t="s">
+        <v>547</v>
+      </c>
+      <c r="N3" s="30"/>
+      <c r="O3" s="37"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B4" s="53"/>
       <c r="C4" s="5">
         <v>2</v>
       </c>
@@ -7043,14 +8364,20 @@
       <c r="J4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="49" t="s">
+        <v>660</v>
+      </c>
+      <c r="L4" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="L4" s="8"/>
-      <c r="M4" s="37"/>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B5" s="47"/>
+      <c r="M4" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N4" s="8"/>
+      <c r="O4" s="37"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B5" s="53"/>
       <c r="C5" s="5">
         <v>3</v>
       </c>
@@ -7075,14 +8402,20 @@
       <c r="J5" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="49" t="s">
+        <v>661</v>
+      </c>
+      <c r="L5" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="L5" s="8"/>
-      <c r="M5" s="37"/>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
+      <c r="M5" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N5" s="8"/>
+      <c r="O5" s="37"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B6" s="53"/>
       <c r="C6" s="5">
         <v>4</v>
       </c>
@@ -7107,14 +8440,20 @@
       <c r="J6" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="49" t="s">
+        <v>662</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="L6" s="8"/>
-      <c r="M6" s="37"/>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
+      <c r="M6" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N6" s="8"/>
+      <c r="O6" s="37"/>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B7" s="53"/>
       <c r="C7" s="21">
         <v>5</v>
       </c>
@@ -7140,13 +8479,19 @@
         <v>356</v>
       </c>
       <c r="K7" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="L7" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="L7" s="8"/>
-      <c r="M7" s="37"/>
-    </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B8" s="47"/>
+      <c r="M7" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N7" s="8"/>
+      <c r="O7" s="37"/>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B8" s="53"/>
       <c r="C8" s="5">
         <v>6</v>
       </c>
@@ -7171,14 +8516,20 @@
       <c r="J8" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="49" t="s">
+        <v>664</v>
+      </c>
+      <c r="L8" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="L8" s="8"/>
-      <c r="M8" s="37"/>
-    </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
+      <c r="M8" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N8" s="8"/>
+      <c r="O8" s="37"/>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B9" s="53"/>
       <c r="C9" s="5">
         <v>7</v>
       </c>
@@ -7203,14 +8554,20 @@
       <c r="J9" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="49" t="s">
+        <v>665</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="L9" s="8"/>
-      <c r="M9" s="37"/>
-    </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
+      <c r="M9" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N9" s="8"/>
+      <c r="O9" s="37"/>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B10" s="53"/>
       <c r="C10" s="5">
         <v>8</v>
       </c>
@@ -7235,14 +8592,20 @@
       <c r="J10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="49" t="s">
+        <v>666</v>
+      </c>
+      <c r="L10" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="L10" s="8"/>
-      <c r="M10" s="37"/>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B11" s="47"/>
+      <c r="M10" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="N10" s="8"/>
+      <c r="O10" s="37"/>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B11" s="53"/>
       <c r="C11" s="5">
         <v>9</v>
       </c>
@@ -7267,14 +8630,20 @@
       <c r="J11" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="49" t="s">
+        <v>667</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="L11" s="8"/>
-      <c r="M11" s="37"/>
-    </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
+      <c r="M11" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="N11" s="8"/>
+      <c r="O11" s="37"/>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B12" s="54"/>
       <c r="C12" s="9">
         <v>10</v>
       </c>
@@ -7300,13 +8669,19 @@
         <v>32</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="L12" s="8"/>
-      <c r="M12" s="37"/>
-    </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B13" s="49">
+      <c r="M12" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N12" s="8"/>
+      <c r="O12" s="37"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B13" s="55">
         <v>2</v>
       </c>
       <c r="C13" s="12">
@@ -7334,13 +8709,19 @@
         <v>103</v>
       </c>
       <c r="K13" s="13" t="s">
+        <v>669</v>
+      </c>
+      <c r="L13" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="L13" s="8"/>
-      <c r="M13" s="37"/>
-    </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B14" s="47"/>
+      <c r="M13" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N13" s="8"/>
+      <c r="O13" s="37"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B14" s="53"/>
       <c r="C14" s="5">
         <v>2</v>
       </c>
@@ -7365,14 +8746,20 @@
       <c r="J14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K14" s="6" t="s">
+      <c r="K14" s="49" t="s">
+        <v>670</v>
+      </c>
+      <c r="L14" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="L14" s="8"/>
-      <c r="M14" s="37"/>
-    </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
+      <c r="M14" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N14" s="8"/>
+      <c r="O14" s="37"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B15" s="53"/>
       <c r="C15" s="5">
         <v>3</v>
       </c>
@@ -7397,14 +8784,20 @@
       <c r="J15" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="K15" s="6" t="s">
+      <c r="K15" s="49" t="s">
+        <v>671</v>
+      </c>
+      <c r="L15" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="L15" s="8"/>
-      <c r="M15" s="37"/>
-    </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
+      <c r="M15" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N15" s="8"/>
+      <c r="O15" s="37"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B16" s="53"/>
       <c r="C16" s="5">
         <v>4</v>
       </c>
@@ -7429,14 +8822,20 @@
       <c r="J16" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="49" t="s">
+        <v>672</v>
+      </c>
+      <c r="L16" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="37"/>
-    </row>
-    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B17" s="47"/>
+      <c r="M16" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N16" s="8"/>
+      <c r="O16" s="37"/>
+    </row>
+    <row r="17" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B17" s="53"/>
       <c r="C17" s="21">
         <v>5</v>
       </c>
@@ -7462,13 +8861,19 @@
         <v>375</v>
       </c>
       <c r="K17" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="L17" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="37"/>
-    </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B18" s="47"/>
+      <c r="M17" s="49" t="s">
+        <v>554</v>
+      </c>
+      <c r="N17" s="8"/>
+      <c r="O17" s="37"/>
+    </row>
+    <row r="18" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B18" s="53"/>
       <c r="C18" s="5">
         <v>6</v>
       </c>
@@ -7493,14 +8898,20 @@
       <c r="J18" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="49" t="s">
+        <v>674</v>
+      </c>
+      <c r="L18" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="L18" s="8"/>
-      <c r="M18" s="37"/>
-    </row>
-    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="47"/>
+      <c r="M18" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N18" s="8"/>
+      <c r="O18" s="37"/>
+    </row>
+    <row r="19" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B19" s="53"/>
       <c r="C19" s="5">
         <v>7</v>
       </c>
@@ -7525,14 +8936,20 @@
       <c r="J19" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="K19" s="6" t="s">
+      <c r="K19" s="49" t="s">
+        <v>675</v>
+      </c>
+      <c r="L19" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="L19" s="8"/>
-      <c r="M19" s="37"/>
-    </row>
-    <row r="20" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B20" s="47"/>
+      <c r="M19" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N19" s="8"/>
+      <c r="O19" s="37"/>
+    </row>
+    <row r="20" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B20" s="53"/>
       <c r="C20" s="5">
         <v>8</v>
       </c>
@@ -7557,14 +8974,20 @@
       <c r="J20" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="K20" s="6" t="s">
+      <c r="K20" s="49" t="s">
+        <v>676</v>
+      </c>
+      <c r="L20" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="L20" s="8"/>
-      <c r="M20" s="37"/>
-    </row>
-    <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="47"/>
+      <c r="M20" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N20" s="8"/>
+      <c r="O20" s="37"/>
+    </row>
+    <row r="21" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B21" s="53"/>
       <c r="C21" s="5">
         <v>9</v>
       </c>
@@ -7589,14 +9012,20 @@
       <c r="J21" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="K21" s="6" t="s">
+      <c r="K21" s="49" t="s">
+        <v>677</v>
+      </c>
+      <c r="L21" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="L21" s="8"/>
-      <c r="M21" s="37"/>
-    </row>
-    <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="48"/>
+      <c r="M21" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N21" s="8"/>
+      <c r="O21" s="37"/>
+    </row>
+    <row r="22" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B22" s="54"/>
       <c r="C22" s="9">
         <v>10</v>
       </c>
@@ -7622,13 +9051,19 @@
         <v>122</v>
       </c>
       <c r="K22" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="L22" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="L22" s="8"/>
-      <c r="M22" s="37"/>
-    </row>
-    <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="49">
+      <c r="M22" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N22" s="8"/>
+      <c r="O22" s="37"/>
+    </row>
+    <row r="23" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B23" s="55">
         <v>3</v>
       </c>
       <c r="C23" s="12">
@@ -7656,13 +9091,19 @@
         <v>103</v>
       </c>
       <c r="K23" s="13" t="s">
+        <v>679</v>
+      </c>
+      <c r="L23" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="L23" s="8"/>
-      <c r="M23" s="37"/>
-    </row>
-    <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="47"/>
+      <c r="M23" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N23" s="8"/>
+      <c r="O23" s="37"/>
+    </row>
+    <row r="24" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B24" s="53"/>
       <c r="C24" s="5">
         <v>2</v>
       </c>
@@ -7687,14 +9128,20 @@
       <c r="J24" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="K24" s="6" t="s">
+      <c r="K24" s="49" t="s">
+        <v>680</v>
+      </c>
+      <c r="L24" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="L24" s="8"/>
-      <c r="M24" s="37"/>
-    </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="47"/>
+      <c r="M24" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N24" s="8"/>
+      <c r="O24" s="37"/>
+    </row>
+    <row r="25" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B25" s="53"/>
       <c r="C25" s="5">
         <v>3</v>
       </c>
@@ -7719,14 +9166,20 @@
       <c r="J25" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K25" s="6" t="s">
+      <c r="K25" s="49" t="s">
+        <v>681</v>
+      </c>
+      <c r="L25" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="37"/>
-    </row>
-    <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="47"/>
+      <c r="M25" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N25" s="8"/>
+      <c r="O25" s="37"/>
+    </row>
+    <row r="26" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B26" s="53"/>
       <c r="C26" s="5">
         <v>4</v>
       </c>
@@ -7751,14 +9204,20 @@
       <c r="J26" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K26" s="6" t="s">
+      <c r="K26" s="49" t="s">
+        <v>682</v>
+      </c>
+      <c r="L26" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="37"/>
-    </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="47"/>
+      <c r="M26" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N26" s="8"/>
+      <c r="O26" s="37"/>
+    </row>
+    <row r="27" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B27" s="53"/>
       <c r="C27" s="21">
         <v>5</v>
       </c>
@@ -7784,13 +9243,19 @@
         <v>390</v>
       </c>
       <c r="K27" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="L27" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="L27" s="8"/>
-      <c r="M27" s="37"/>
-    </row>
-    <row r="28" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="47"/>
+      <c r="M27" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N27" s="8"/>
+      <c r="O27" s="37"/>
+    </row>
+    <row r="28" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B28" s="53"/>
       <c r="C28" s="5">
         <v>6</v>
       </c>
@@ -7815,14 +9280,20 @@
       <c r="J28" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K28" s="6" t="s">
+      <c r="K28" s="49" t="s">
+        <v>684</v>
+      </c>
+      <c r="L28" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="L28" s="8"/>
-      <c r="M28" s="37"/>
-    </row>
-    <row r="29" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="47"/>
+      <c r="M28" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N28" s="8"/>
+      <c r="O28" s="37"/>
+    </row>
+    <row r="29" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B29" s="53"/>
       <c r="C29" s="5">
         <v>7</v>
       </c>
@@ -7847,14 +9318,20 @@
       <c r="J29" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="K29" s="6" t="s">
+      <c r="K29" s="49" t="s">
+        <v>685</v>
+      </c>
+      <c r="L29" s="6" t="s">
         <v>393</v>
       </c>
-      <c r="L29" s="8"/>
-      <c r="M29" s="37"/>
-    </row>
-    <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="47"/>
+      <c r="M29" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="N29" s="8"/>
+      <c r="O29" s="37"/>
+    </row>
+    <row r="30" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B30" s="53"/>
       <c r="C30" s="5">
         <v>8</v>
       </c>
@@ -7879,14 +9356,20 @@
       <c r="J30" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="K30" s="6" t="s">
+      <c r="K30" s="49" t="s">
+        <v>686</v>
+      </c>
+      <c r="L30" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="L30" s="8"/>
-      <c r="M30" s="37"/>
-    </row>
-    <row r="31" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B31" s="47"/>
+      <c r="M30" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N30" s="8"/>
+      <c r="O30" s="37"/>
+    </row>
+    <row r="31" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B31" s="53"/>
       <c r="C31" s="5">
         <v>9</v>
       </c>
@@ -7911,14 +9394,20 @@
       <c r="J31" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="K31" s="6" t="s">
+      <c r="K31" s="49" t="s">
+        <v>687</v>
+      </c>
+      <c r="L31" s="6" t="s">
         <v>397</v>
       </c>
-      <c r="L31" s="8"/>
-      <c r="M31" s="37"/>
-    </row>
-    <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="48"/>
+      <c r="M31" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N31" s="8"/>
+      <c r="O31" s="37"/>
+    </row>
+    <row r="32" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B32" s="54"/>
       <c r="C32" s="9">
         <v>10</v>
       </c>
@@ -7944,13 +9433,19 @@
         <v>32</v>
       </c>
       <c r="K32" s="10" t="s">
+        <v>688</v>
+      </c>
+      <c r="L32" s="10" t="s">
         <v>399</v>
       </c>
-      <c r="L32" s="8"/>
-      <c r="M32" s="37"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B33" s="49">
+      <c r="M32" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N32" s="8"/>
+      <c r="O32" s="37"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B33" s="55">
         <v>4</v>
       </c>
       <c r="C33" s="12">
@@ -7978,13 +9473,19 @@
         <v>103</v>
       </c>
       <c r="K33" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="L33" s="13" t="s">
         <v>349</v>
       </c>
-      <c r="L33" s="8"/>
-      <c r="M33" s="37"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
+      <c r="M33" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N33" s="8"/>
+      <c r="O33" s="37"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B34" s="53"/>
       <c r="C34" s="5">
         <v>2</v>
       </c>
@@ -8009,14 +9510,20 @@
       <c r="J34" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="K34" s="6" t="s">
+      <c r="K34" s="49" t="s">
+        <v>690</v>
+      </c>
+      <c r="L34" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="L34" s="8"/>
-      <c r="M34" s="37"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B35" s="47"/>
+      <c r="M34" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N34" s="8"/>
+      <c r="O34" s="37"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B35" s="53"/>
       <c r="C35" s="5">
         <v>3</v>
       </c>
@@ -8041,14 +9548,20 @@
       <c r="J35" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K35" s="6" t="s">
+      <c r="K35" s="49" t="s">
+        <v>691</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="L35" s="8"/>
-      <c r="M35" s="37"/>
-    </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
+      <c r="M35" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="N35" s="8"/>
+      <c r="O35" s="37"/>
+    </row>
+    <row r="36" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B36" s="53"/>
       <c r="C36" s="5">
         <v>4</v>
       </c>
@@ -8073,14 +9586,20 @@
       <c r="J36" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="K36" s="6" t="s">
+      <c r="K36" s="49" t="s">
+        <v>692</v>
+      </c>
+      <c r="L36" s="6" t="s">
         <v>401</v>
       </c>
-      <c r="L36" s="8"/>
-      <c r="M36" s="37"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B37" s="47"/>
+      <c r="M36" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N36" s="8"/>
+      <c r="O36" s="37"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B37" s="53"/>
       <c r="C37" s="21">
         <v>5</v>
       </c>
@@ -8106,13 +9625,19 @@
         <v>390</v>
       </c>
       <c r="K37" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="L37" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="L37" s="8"/>
-      <c r="M37" s="37"/>
-    </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
+      <c r="M37" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N37" s="8"/>
+      <c r="O37" s="37"/>
+    </row>
+    <row r="38" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B38" s="53"/>
       <c r="C38" s="5">
         <v>6</v>
       </c>
@@ -8137,14 +9662,20 @@
       <c r="J38" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K38" s="6" t="s">
+      <c r="K38" s="49" t="s">
+        <v>694</v>
+      </c>
+      <c r="L38" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="L38" s="8"/>
-      <c r="M38" s="37"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B39" s="47"/>
+      <c r="M38" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N38" s="8"/>
+      <c r="O38" s="37"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B39" s="53"/>
       <c r="C39" s="5">
         <v>7</v>
       </c>
@@ -8169,14 +9700,20 @@
       <c r="J39" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="K39" s="6" t="s">
+      <c r="K39" s="49" t="s">
+        <v>695</v>
+      </c>
+      <c r="L39" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="L39" s="8"/>
-      <c r="M39" s="37"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B40" s="47"/>
+      <c r="M39" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N39" s="8"/>
+      <c r="O39" s="37"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B40" s="53"/>
       <c r="C40" s="5">
         <v>8</v>
       </c>
@@ -8201,14 +9738,20 @@
       <c r="J40" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="K40" s="6" t="s">
+      <c r="K40" s="49" t="s">
+        <v>696</v>
+      </c>
+      <c r="L40" s="6" t="s">
         <v>405</v>
       </c>
-      <c r="L40" s="8"/>
-      <c r="M40" s="37"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B41" s="47"/>
+      <c r="M40" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N40" s="8"/>
+      <c r="O40" s="37"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B41" s="53"/>
       <c r="C41" s="5">
         <v>9</v>
       </c>
@@ -8233,14 +9776,20 @@
       <c r="J41" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="K41" s="6" t="s">
+      <c r="K41" s="49" t="s">
+        <v>697</v>
+      </c>
+      <c r="L41" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="L41" s="8"/>
-      <c r="M41" s="37"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B42" s="48"/>
+      <c r="M41" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N41" s="8"/>
+      <c r="O41" s="37"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B42" s="54"/>
       <c r="C42" s="9">
         <v>10</v>
       </c>
@@ -8266,13 +9815,19 @@
         <v>122</v>
       </c>
       <c r="K42" s="10" t="s">
+        <v>698</v>
+      </c>
+      <c r="L42" s="10" t="s">
         <v>407</v>
       </c>
-      <c r="L42" s="8"/>
-      <c r="M42" s="37"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B43" s="49">
+      <c r="M42" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="N42" s="8"/>
+      <c r="O42" s="37"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B43" s="55">
         <v>5</v>
       </c>
       <c r="C43" s="12">
@@ -8300,13 +9855,19 @@
         <v>103</v>
       </c>
       <c r="K43" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="L43" s="13" t="s">
         <v>369</v>
       </c>
-      <c r="L43" s="8"/>
-      <c r="M43" s="37"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B44" s="47"/>
+      <c r="M43" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N43" s="8"/>
+      <c r="O43" s="37"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B44" s="53"/>
       <c r="C44" s="5">
         <v>2</v>
       </c>
@@ -8331,14 +9892,20 @@
       <c r="J44" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="K44" s="6" t="s">
+      <c r="K44" s="49" t="s">
+        <v>700</v>
+      </c>
+      <c r="L44" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="L44" s="8"/>
-      <c r="M44" s="37"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B45" s="47"/>
+      <c r="M44" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="N44" s="8"/>
+      <c r="O44" s="37"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B45" s="53"/>
       <c r="C45" s="5">
         <v>3</v>
       </c>
@@ -8363,14 +9930,20 @@
       <c r="J45" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K45" s="6" t="s">
+      <c r="K45" s="49" t="s">
+        <v>701</v>
+      </c>
+      <c r="L45" s="6" t="s">
         <v>409</v>
       </c>
-      <c r="L45" s="8"/>
-      <c r="M45" s="37"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B46" s="47"/>
+      <c r="M45" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="N45" s="8"/>
+      <c r="O45" s="37"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B46" s="53"/>
       <c r="C46" s="5">
         <v>4</v>
       </c>
@@ -8395,14 +9968,20 @@
       <c r="J46" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="K46" s="6" t="s">
+      <c r="K46" s="49" t="s">
+        <v>702</v>
+      </c>
+      <c r="L46" s="6" t="s">
         <v>410</v>
       </c>
-      <c r="L46" s="8"/>
-      <c r="M46" s="37"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B47" s="47"/>
+      <c r="M46" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N46" s="8"/>
+      <c r="O46" s="37"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B47" s="53"/>
       <c r="C47" s="21">
         <v>5</v>
       </c>
@@ -8428,13 +10007,19 @@
         <v>390</v>
       </c>
       <c r="K47" s="7" t="s">
+        <v>703</v>
+      </c>
+      <c r="L47" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="L47" s="8"/>
-      <c r="M47" s="37"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B48" s="47"/>
+      <c r="M47" s="49" t="s">
+        <v>553</v>
+      </c>
+      <c r="N47" s="8"/>
+      <c r="O47" s="37"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B48" s="53"/>
       <c r="C48" s="5">
         <v>6</v>
       </c>
@@ -8459,14 +10044,20 @@
       <c r="J48" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K48" s="6" t="s">
+      <c r="K48" s="49" t="s">
+        <v>704</v>
+      </c>
+      <c r="L48" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="L48" s="8"/>
-      <c r="M48" s="37"/>
-    </row>
-    <row r="49" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B49" s="47"/>
+      <c r="M48" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="N48" s="8"/>
+      <c r="O48" s="37"/>
+    </row>
+    <row r="49" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B49" s="53"/>
       <c r="C49" s="5">
         <v>7</v>
       </c>
@@ -8491,14 +10082,20 @@
       <c r="J49" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="K49" s="6" t="s">
+      <c r="K49" s="49" t="s">
+        <v>705</v>
+      </c>
+      <c r="L49" s="6" t="s">
         <v>414</v>
       </c>
-      <c r="L49" s="8"/>
-      <c r="M49" s="37"/>
-    </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B50" s="47"/>
+      <c r="M49" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="N49" s="8"/>
+      <c r="O49" s="37"/>
+    </row>
+    <row r="50" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B50" s="53"/>
       <c r="C50" s="5">
         <v>8</v>
       </c>
@@ -8523,14 +10120,20 @@
       <c r="J50" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="6" t="s">
+      <c r="K50" s="49" t="s">
+        <v>706</v>
+      </c>
+      <c r="L50" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="L50" s="8"/>
-      <c r="M50" s="37"/>
-    </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B51" s="47"/>
+      <c r="M50" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="N50" s="8"/>
+      <c r="O50" s="37"/>
+    </row>
+    <row r="51" spans="2:15" x14ac:dyDescent="0.35">
+      <c r="B51" s="53"/>
       <c r="C51" s="5">
         <v>9</v>
       </c>
@@ -8555,14 +10158,20 @@
       <c r="J51" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="K51" s="6" t="s">
+      <c r="K51" s="49" t="s">
+        <v>707</v>
+      </c>
+      <c r="L51" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="L51" s="8"/>
-      <c r="M51" s="37"/>
-    </row>
-    <row r="52" spans="2:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="50"/>
+      <c r="M51" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="N51" s="8"/>
+      <c r="O51" s="37"/>
+    </row>
+    <row r="52" spans="2:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="56"/>
       <c r="C52" s="5">
         <v>10</v>
       </c>
@@ -8588,469 +10197,475 @@
         <v>365</v>
       </c>
       <c r="K52" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="L52" s="15" t="s">
         <v>418</v>
       </c>
-      <c r="L52" s="36"/>
-      <c r="M52" s="37"/>
-    </row>
-    <row r="53" spans="2:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="15" t="s">
+        <v>547</v>
+      </c>
+      <c r="N52" s="36"/>
+      <c r="O52" s="37"/>
+    </row>
+    <row r="53" spans="2:15" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="20"/>
-      <c r="L53" s="17"/>
-    </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="N53" s="17"/>
+    </row>
+    <row r="54" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:15" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
       <c r="E57" s="19"/>
       <c r="F57" s="19"/>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
     </row>
-    <row r="59" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
     </row>
-    <row r="61" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
       <c r="E61" s="19"/>
       <c r="F61" s="19"/>
     </row>
-    <row r="62" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
     </row>
-    <row r="63" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:15" x14ac:dyDescent="0.35">
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
       <c r="E63" s="19"/>
       <c r="F63" s="19"/>
     </row>
-    <row r="64" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
-    </row>
-    <row r="65" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+    </row>
+    <row r="65" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
-    </row>
-    <row r="66" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+    </row>
+    <row r="66" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
-      <c r="L66" s="18"/>
-      <c r="M66" s="18"/>
-    </row>
-    <row r="67" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+    </row>
+    <row r="67" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
-    </row>
-    <row r="68" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+    </row>
+    <row r="68" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
-    </row>
-    <row r="69" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+    </row>
+    <row r="69" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="19"/>
       <c r="F69" s="19"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
-    </row>
-    <row r="70" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+    </row>
+    <row r="70" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
       <c r="E70" s="19"/>
       <c r="F70" s="19"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
-    </row>
-    <row r="71" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+    </row>
+    <row r="71" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="19"/>
       <c r="F71" s="19"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
-    </row>
-    <row r="72" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+    </row>
+    <row r="72" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
       <c r="E72" s="19"/>
       <c r="F72" s="19"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
-    </row>
-    <row r="73" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+    </row>
+    <row r="73" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
-    </row>
-    <row r="74" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+    </row>
+    <row r="74" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
       <c r="F74" s="19"/>
-      <c r="L74" s="18"/>
-      <c r="M74" s="18"/>
-    </row>
-    <row r="75" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+    </row>
+    <row r="75" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="19"/>
       <c r="F75" s="19"/>
-      <c r="L75" s="18"/>
-      <c r="M75" s="18"/>
-    </row>
-    <row r="76" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+    </row>
+    <row r="76" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
-      <c r="L76" s="18"/>
-      <c r="M76" s="18"/>
-    </row>
-    <row r="77" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+    </row>
+    <row r="77" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="19"/>
       <c r="F77" s="19"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
-    </row>
-    <row r="78" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+    </row>
+    <row r="78" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
       <c r="E78" s="19"/>
       <c r="F78" s="19"/>
-      <c r="L78" s="18"/>
-      <c r="M78" s="18"/>
-    </row>
-    <row r="79" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
+    </row>
+    <row r="79" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
       <c r="E79" s="19"/>
       <c r="F79" s="19"/>
-      <c r="L79" s="18"/>
-      <c r="M79" s="18"/>
-    </row>
-    <row r="80" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N79" s="18"/>
+      <c r="O79" s="18"/>
+    </row>
+    <row r="80" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="19"/>
       <c r="F80" s="19"/>
-      <c r="L80" s="18"/>
-      <c r="M80" s="18"/>
-    </row>
-    <row r="81" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
+    </row>
+    <row r="81" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
       <c r="E81" s="19"/>
       <c r="F81" s="19"/>
-      <c r="L81" s="18"/>
-      <c r="M81" s="18"/>
-    </row>
-    <row r="82" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+    </row>
+    <row r="82" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
       <c r="E82" s="19"/>
       <c r="F82" s="19"/>
-      <c r="L82" s="18"/>
-      <c r="M82" s="18"/>
-    </row>
-    <row r="83" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+    </row>
+    <row r="83" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="19"/>
       <c r="F83" s="19"/>
-      <c r="L83" s="18"/>
-      <c r="M83" s="18"/>
-    </row>
-    <row r="84" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+    </row>
+    <row r="84" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
-      <c r="L84" s="18"/>
-      <c r="M84" s="18"/>
-    </row>
-    <row r="85" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
+    </row>
+    <row r="85" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
       <c r="E85" s="19"/>
       <c r="F85" s="19"/>
-      <c r="L85" s="18"/>
-      <c r="M85" s="18"/>
-    </row>
-    <row r="86" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
+    </row>
+    <row r="86" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
       <c r="E86" s="19"/>
       <c r="F86" s="19"/>
-      <c r="L86" s="18"/>
-      <c r="M86" s="18"/>
-    </row>
-    <row r="87" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
+    </row>
+    <row r="87" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
-      <c r="L87" s="18"/>
-      <c r="M87" s="18"/>
-    </row>
-    <row r="88" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
+    </row>
+    <row r="88" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
-      <c r="L88" s="18"/>
-      <c r="M88" s="18"/>
-    </row>
-    <row r="89" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+    </row>
+    <row r="89" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
       <c r="E89" s="19"/>
       <c r="F89" s="19"/>
-      <c r="L89" s="18"/>
-      <c r="M89" s="18"/>
-    </row>
-    <row r="90" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+    </row>
+    <row r="90" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
       <c r="E90" s="19"/>
       <c r="F90" s="19"/>
-      <c r="L90" s="18"/>
-      <c r="M90" s="18"/>
-    </row>
-    <row r="91" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N90" s="18"/>
+      <c r="O90" s="18"/>
+    </row>
+    <row r="91" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
-      <c r="L91" s="18"/>
-      <c r="M91" s="18"/>
-    </row>
-    <row r="92" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
+    </row>
+    <row r="92" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
       <c r="E92" s="19"/>
       <c r="F92" s="19"/>
-      <c r="L92" s="18"/>
-      <c r="M92" s="18"/>
-    </row>
-    <row r="93" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
+    </row>
+    <row r="93" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
       <c r="E93" s="19"/>
       <c r="F93" s="19"/>
-      <c r="L93" s="18"/>
-      <c r="M93" s="18"/>
-    </row>
-    <row r="94" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="18"/>
+      <c r="O93" s="18"/>
+    </row>
+    <row r="94" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
       <c r="E94" s="19"/>
       <c r="F94" s="19"/>
-      <c r="L94" s="18"/>
-      <c r="M94" s="18"/>
-    </row>
-    <row r="95" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N94" s="18"/>
+      <c r="O94" s="18"/>
+    </row>
+    <row r="95" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="19"/>
       <c r="F95" s="19"/>
-      <c r="L95" s="18"/>
-      <c r="M95" s="18"/>
-    </row>
-    <row r="96" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N95" s="18"/>
+      <c r="O95" s="18"/>
+    </row>
+    <row r="96" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
-      <c r="L96" s="18"/>
-      <c r="M96" s="18"/>
-    </row>
-    <row r="97" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N96" s="18"/>
+      <c r="O96" s="18"/>
+    </row>
+    <row r="97" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
-      <c r="L97" s="18"/>
-      <c r="M97" s="18"/>
-    </row>
-    <row r="98" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="18"/>
+      <c r="O97" s="18"/>
+    </row>
+    <row r="98" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
       <c r="E98" s="19"/>
       <c r="F98" s="19"/>
-      <c r="L98" s="18"/>
-      <c r="M98" s="18"/>
-    </row>
-    <row r="99" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N98" s="18"/>
+      <c r="O98" s="18"/>
+    </row>
+    <row r="99" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
       <c r="E99" s="19"/>
       <c r="F99" s="19"/>
-      <c r="L99" s="18"/>
-      <c r="M99" s="18"/>
-    </row>
-    <row r="100" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N99" s="18"/>
+      <c r="O99" s="18"/>
+    </row>
+    <row r="100" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="19"/>
       <c r="F100" s="19"/>
-      <c r="L100" s="18"/>
-      <c r="M100" s="18"/>
-    </row>
-    <row r="101" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N100" s="18"/>
+      <c r="O100" s="18"/>
+    </row>
+    <row r="101" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="L101" s="18"/>
-      <c r="M101" s="18"/>
-    </row>
-    <row r="102" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N101" s="18"/>
+      <c r="O101" s="18"/>
+    </row>
+    <row r="102" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="19"/>
       <c r="F102" s="19"/>
-      <c r="L102" s="18"/>
-      <c r="M102" s="18"/>
-    </row>
-    <row r="103" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="18"/>
+      <c r="O102" s="18"/>
+    </row>
+    <row r="103" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
-      <c r="L103" s="18"/>
-      <c r="M103" s="18"/>
-    </row>
-    <row r="104" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N103" s="18"/>
+      <c r="O103" s="18"/>
+    </row>
+    <row r="104" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
-      <c r="L104" s="18"/>
-      <c r="M104" s="18"/>
-    </row>
-    <row r="105" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N104" s="18"/>
+      <c r="O104" s="18"/>
+    </row>
+    <row r="105" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
       <c r="D105" s="19"/>
       <c r="E105" s="19"/>
       <c r="F105" s="19"/>
-      <c r="L105" s="18"/>
-      <c r="M105" s="18"/>
-    </row>
-    <row r="106" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N105" s="18"/>
+      <c r="O105" s="18"/>
+    </row>
+    <row r="106" spans="2:15" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
       <c r="D106" s="19"/>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
-      <c r="L106" s="18"/>
-      <c r="M106" s="18"/>
+      <c r="N106" s="18"/>
+      <c r="O106" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9066,33 +10681,35 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:L106"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:N106"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.81640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.453125" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="100.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="44.28515625" style="18" customWidth="1"/>
-    <col min="13" max="13" width="6.85546875" customWidth="1"/>
-    <col min="14" max="14" width="3.140625" customWidth="1"/>
-    <col min="15" max="15" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.42578125" customWidth="1"/>
-    <col min="17" max="17" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="30.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2" customWidth="1"/>
+    <col min="11" max="11" width="19" style="3" customWidth="1"/>
+    <col min="12" max="12" width="100.7265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="39" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.26953125" style="18" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.81640625" customWidth="1"/>
+    <col min="16" max="16" width="3.1796875" customWidth="1"/>
+    <col min="17" max="17" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.453125" customWidth="1"/>
+    <col min="19" max="19" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="46.1796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -9103,9 +10720,11 @@
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="4"/>
-    </row>
-    <row r="2" spans="2:12" ht="17.25" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="4"/>
+    </row>
+    <row r="2" spans="2:14" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B2" s="22" t="s">
         <v>0</v>
       </c>
@@ -9134,14 +10753,20 @@
         <v>9</v>
       </c>
       <c r="K2" s="23" t="s">
+        <v>558</v>
+      </c>
+      <c r="L2" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="26" t="s">
+      <c r="M2" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="N2" s="26" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="47">
+    <row r="3" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="53">
         <v>1</v>
       </c>
       <c r="C3" s="5">
@@ -9168,13 +10793,19 @@
       <c r="J3" s="29" t="s">
         <v>432</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="28" t="s">
+        <v>709</v>
+      </c>
+      <c r="L3" s="44" t="s">
         <v>433</v>
       </c>
-      <c r="L3"/>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="47"/>
+      <c r="M3" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N3"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B4" s="53"/>
       <c r="C4" s="5">
         <v>2</v>
       </c>
@@ -9199,13 +10830,19 @@
       <c r="J4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K4" s="52" t="s">
+      <c r="K4" s="49" t="s">
+        <v>710</v>
+      </c>
+      <c r="L4" s="45" t="s">
         <v>436</v>
       </c>
-      <c r="L4"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="47"/>
+      <c r="M4" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N4"/>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B5" s="53"/>
       <c r="C5" s="5">
         <v>3</v>
       </c>
@@ -9230,13 +10867,19 @@
       <c r="J5" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K5" s="52" t="s">
+      <c r="K5" s="49" t="s">
+        <v>711</v>
+      </c>
+      <c r="L5" s="45" t="s">
         <v>441</v>
       </c>
-      <c r="L5"/>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="47"/>
+      <c r="M5" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B6" s="53"/>
       <c r="C6" s="5">
         <v>4</v>
       </c>
@@ -9261,13 +10904,19 @@
       <c r="J6" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="49" t="s">
+        <v>712</v>
+      </c>
+      <c r="L6" s="45" t="s">
         <v>445</v>
       </c>
-      <c r="L6"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="47"/>
+      <c r="M6" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="N6"/>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B7" s="53"/>
       <c r="C7" s="21">
         <v>5</v>
       </c>
@@ -9292,13 +10941,19 @@
       <c r="J7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K7" s="52" t="s">
+      <c r="K7" s="49" t="s">
+        <v>713</v>
+      </c>
+      <c r="L7" s="45" t="s">
         <v>447</v>
       </c>
-      <c r="L7"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="47"/>
+      <c r="M7" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N7"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B8" s="53"/>
       <c r="C8" s="5">
         <v>6</v>
       </c>
@@ -9323,13 +10978,19 @@
       <c r="J8" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="K8" s="52" t="s">
+      <c r="K8" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="L8" s="45" t="s">
         <v>452</v>
       </c>
-      <c r="L8"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="47"/>
+      <c r="M8" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N8"/>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B9" s="53"/>
       <c r="C9" s="5">
         <v>7</v>
       </c>
@@ -9354,13 +11015,19 @@
       <c r="J9" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="K9" s="52" t="s">
+      <c r="K9" s="49" t="s">
+        <v>715</v>
+      </c>
+      <c r="L9" s="45" t="s">
         <v>456</v>
       </c>
-      <c r="L9"/>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="47"/>
+      <c r="M9" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N9"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B10" s="53"/>
       <c r="C10" s="5">
         <v>8</v>
       </c>
@@ -9385,13 +11052,19 @@
       <c r="J10" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="K10" s="52" t="s">
+      <c r="K10" s="49" t="s">
+        <v>716</v>
+      </c>
+      <c r="L10" s="45" t="s">
         <v>459</v>
       </c>
-      <c r="L10"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="47"/>
+      <c r="M10" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N10"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B11" s="53"/>
       <c r="C11" s="5">
         <v>9</v>
       </c>
@@ -9416,13 +11089,19 @@
       <c r="J11" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="K11" s="52" t="s">
+      <c r="K11" s="49" t="s">
+        <v>717</v>
+      </c>
+      <c r="L11" s="45" t="s">
         <v>464</v>
       </c>
-      <c r="L11"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
+      <c r="M11" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B12" s="54"/>
       <c r="C12" s="9">
         <v>10</v>
       </c>
@@ -9447,13 +11126,19 @@
       <c r="J12" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="K12" s="53" t="s">
+      <c r="K12" s="10" t="s">
+        <v>718</v>
+      </c>
+      <c r="L12" s="46" t="s">
         <v>468</v>
       </c>
-      <c r="L12"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="49">
+      <c r="M12" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N12"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B13" s="55">
         <v>2</v>
       </c>
       <c r="C13" s="12">
@@ -9480,13 +11165,19 @@
       <c r="J13" s="14" t="s">
         <v>463</v>
       </c>
-      <c r="K13" s="54" t="s">
+      <c r="K13" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="L13" s="47" t="s">
         <v>469</v>
       </c>
-      <c r="L13"/>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="47"/>
+      <c r="M13" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="N13"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B14" s="53"/>
       <c r="C14" s="5">
         <v>2</v>
       </c>
@@ -9511,13 +11202,19 @@
       <c r="J14" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K14" s="52" t="s">
+      <c r="K14" s="49" t="s">
+        <v>720</v>
+      </c>
+      <c r="L14" s="45" t="s">
         <v>470</v>
       </c>
-      <c r="L14"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="47"/>
+      <c r="M14" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N14"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B15" s="53"/>
       <c r="C15" s="5">
         <v>3</v>
       </c>
@@ -9542,13 +11239,19 @@
       <c r="J15" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="52" t="s">
+      <c r="K15" s="49" t="s">
+        <v>721</v>
+      </c>
+      <c r="L15" s="45" t="s">
         <v>473</v>
       </c>
-      <c r="L15"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="47"/>
+      <c r="M15" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N15"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B16" s="53"/>
       <c r="C16" s="5">
         <v>4</v>
       </c>
@@ -9573,13 +11276,19 @@
       <c r="J16" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="K16" s="52" t="s">
+      <c r="K16" s="49" t="s">
+        <v>722</v>
+      </c>
+      <c r="L16" s="45" t="s">
         <v>476</v>
       </c>
-      <c r="L16"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B17" s="47"/>
+      <c r="M16" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N16"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B17" s="53"/>
       <c r="C17" s="21">
         <v>5</v>
       </c>
@@ -9604,13 +11313,19 @@
       <c r="J17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="52" t="s">
+      <c r="K17" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="L17" s="45" t="s">
         <v>477</v>
       </c>
-      <c r="L17"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="47"/>
+      <c r="M17" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="N17"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B18" s="53"/>
       <c r="C18" s="5">
         <v>6</v>
       </c>
@@ -9635,13 +11350,19 @@
       <c r="J18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K18" s="52" t="s">
+      <c r="K18" s="49" t="s">
+        <v>724</v>
+      </c>
+      <c r="L18" s="45" t="s">
         <v>478</v>
       </c>
-      <c r="L18"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="47"/>
+      <c r="M18" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N18"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B19" s="53"/>
       <c r="C19" s="5">
         <v>7</v>
       </c>
@@ -9666,13 +11387,19 @@
       <c r="J19" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="K19" s="52" t="s">
+      <c r="K19" s="49" t="s">
+        <v>725</v>
+      </c>
+      <c r="L19" s="45" t="s">
         <v>481</v>
       </c>
-      <c r="L19"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="47"/>
+      <c r="M19" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="N19"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B20" s="53"/>
       <c r="C20" s="5">
         <v>8</v>
       </c>
@@ -9697,13 +11424,19 @@
       <c r="J20" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="K20" s="52" t="s">
+      <c r="K20" s="49" t="s">
+        <v>726</v>
+      </c>
+      <c r="L20" s="45" t="s">
         <v>483</v>
       </c>
-      <c r="L20"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="47"/>
+      <c r="M20" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N20"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B21" s="53"/>
       <c r="C21" s="5">
         <v>9</v>
       </c>
@@ -9728,13 +11461,19 @@
       <c r="J21" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="K21" s="52" t="s">
+      <c r="K21" s="49" t="s">
+        <v>727</v>
+      </c>
+      <c r="L21" s="45" t="s">
         <v>485</v>
       </c>
-      <c r="L21"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="48"/>
+      <c r="M21" s="49" t="s">
+        <v>554</v>
+      </c>
+      <c r="N21"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B22" s="54"/>
       <c r="C22" s="9">
         <v>10</v>
       </c>
@@ -9759,13 +11498,19 @@
       <c r="J22" s="11" t="s">
         <v>488</v>
       </c>
-      <c r="K22" s="53" t="s">
+      <c r="K22" s="10" t="s">
+        <v>728</v>
+      </c>
+      <c r="L22" s="46" t="s">
         <v>489</v>
       </c>
-      <c r="L22"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="49">
+      <c r="M22" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N22"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B23" s="55">
         <v>3</v>
       </c>
       <c r="C23" s="12">
@@ -9792,13 +11537,19 @@
       <c r="J23" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="K23" s="54" t="s">
+      <c r="K23" s="13" t="s">
+        <v>729</v>
+      </c>
+      <c r="L23" s="47" t="s">
         <v>492</v>
       </c>
-      <c r="L23"/>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="47"/>
+      <c r="M23" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N23"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B24" s="53"/>
       <c r="C24" s="5">
         <v>2</v>
       </c>
@@ -9823,13 +11574,19 @@
       <c r="J24" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="K24" s="52" t="s">
+      <c r="K24" s="49" t="s">
+        <v>730</v>
+      </c>
+      <c r="L24" s="45" t="s">
         <v>493</v>
       </c>
-      <c r="L24"/>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="47"/>
+      <c r="M24" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N24"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B25" s="53"/>
       <c r="C25" s="5">
         <v>3</v>
       </c>
@@ -9854,13 +11611,19 @@
       <c r="J25" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K25" s="52" t="s">
+      <c r="K25" s="49" t="s">
+        <v>731</v>
+      </c>
+      <c r="L25" s="45" t="s">
         <v>494</v>
       </c>
-      <c r="L25"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="47"/>
+      <c r="M25" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="N25"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B26" s="53"/>
       <c r="C26" s="5">
         <v>4</v>
       </c>
@@ -9885,13 +11648,19 @@
       <c r="J26" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="K26" s="52" t="s">
+      <c r="K26" s="49" t="s">
+        <v>732</v>
+      </c>
+      <c r="L26" s="45" t="s">
         <v>495</v>
       </c>
-      <c r="L26"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="47"/>
+      <c r="M26" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="N26"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B27" s="53"/>
       <c r="C27" s="21">
         <v>5</v>
       </c>
@@ -9916,13 +11685,19 @@
       <c r="J27" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="K27" s="52" t="s">
+      <c r="K27" s="49" t="s">
+        <v>733</v>
+      </c>
+      <c r="L27" s="45" t="s">
         <v>497</v>
       </c>
-      <c r="L27"/>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="47"/>
+      <c r="M27" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N27"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B28" s="53"/>
       <c r="C28" s="5">
         <v>6</v>
       </c>
@@ -9947,13 +11722,19 @@
       <c r="J28" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="K28" s="52" t="s">
+      <c r="K28" s="49" t="s">
+        <v>734</v>
+      </c>
+      <c r="L28" s="45" t="s">
         <v>499</v>
       </c>
-      <c r="L28"/>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="47"/>
+      <c r="M28" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="N28"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B29" s="53"/>
       <c r="C29" s="5">
         <v>7</v>
       </c>
@@ -9978,13 +11759,19 @@
       <c r="J29" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K29" s="52" t="s">
+      <c r="K29" s="49" t="s">
+        <v>735</v>
+      </c>
+      <c r="L29" s="45" t="s">
         <v>501</v>
       </c>
-      <c r="L29"/>
-    </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B30" s="47"/>
+      <c r="M29" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="N29"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B30" s="53"/>
       <c r="C30" s="5">
         <v>8</v>
       </c>
@@ -10009,13 +11796,19 @@
       <c r="J30" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="K30" s="52" t="s">
+      <c r="K30" s="49" t="s">
+        <v>736</v>
+      </c>
+      <c r="L30" s="45" t="s">
         <v>502</v>
       </c>
-      <c r="L30"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="47"/>
+      <c r="M30" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N30"/>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B31" s="53"/>
       <c r="C31" s="5">
         <v>9</v>
       </c>
@@ -10040,13 +11833,19 @@
       <c r="J31" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="K31" s="52" t="s">
+      <c r="K31" s="49" t="s">
+        <v>737</v>
+      </c>
+      <c r="L31" s="45" t="s">
         <v>504</v>
       </c>
-      <c r="L31"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="48"/>
+      <c r="M31" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N31"/>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B32" s="54"/>
       <c r="C32" s="9">
         <v>10</v>
       </c>
@@ -10071,13 +11870,19 @@
       <c r="J32" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="53" t="s">
+      <c r="K32" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="L32" s="46" t="s">
         <v>505</v>
       </c>
-      <c r="L32"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B33" s="49">
+      <c r="M32" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B33" s="55">
         <v>4</v>
       </c>
       <c r="C33" s="12">
@@ -10104,13 +11909,19 @@
       <c r="J33" s="14" t="s">
         <v>506</v>
       </c>
-      <c r="K33" s="54" t="s">
+      <c r="K33" s="13" t="s">
+        <v>739</v>
+      </c>
+      <c r="L33" s="47" t="s">
         <v>507</v>
       </c>
-      <c r="L33"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B34" s="47"/>
+      <c r="M33" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N33"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B34" s="53"/>
       <c r="C34" s="5">
         <v>2</v>
       </c>
@@ -10135,13 +11946,19 @@
       <c r="J34" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K34" s="52" t="s">
+      <c r="K34" s="49" t="s">
+        <v>740</v>
+      </c>
+      <c r="L34" s="45" t="s">
         <v>509</v>
       </c>
-      <c r="L34"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B35" s="47"/>
+      <c r="M34" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N34"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B35" s="53"/>
       <c r="C35" s="5">
         <v>3</v>
       </c>
@@ -10166,13 +11983,19 @@
       <c r="J35" s="7" t="s">
         <v>510</v>
       </c>
-      <c r="K35" s="52" t="s">
+      <c r="K35" s="49" t="s">
+        <v>741</v>
+      </c>
+      <c r="L35" s="45" t="s">
         <v>511</v>
       </c>
-      <c r="L35"/>
-    </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B36" s="47"/>
+      <c r="M35" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N35"/>
+    </row>
+    <row r="36" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B36" s="53"/>
       <c r="C36" s="5">
         <v>4</v>
       </c>
@@ -10197,13 +12020,19 @@
       <c r="J36" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="K36" s="52" t="s">
+      <c r="K36" s="49" t="s">
+        <v>742</v>
+      </c>
+      <c r="L36" s="45" t="s">
         <v>512</v>
       </c>
-      <c r="L36"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="47"/>
+      <c r="M36" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N36"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B37" s="53"/>
       <c r="C37" s="21">
         <v>5</v>
       </c>
@@ -10228,13 +12057,19 @@
       <c r="J37" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="K37" s="52" t="s">
+      <c r="K37" s="49" t="s">
+        <v>743</v>
+      </c>
+      <c r="L37" s="45" t="s">
         <v>515</v>
       </c>
-      <c r="L37"/>
-    </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B38" s="47"/>
+      <c r="M37" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="N37"/>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B38" s="53"/>
       <c r="C38" s="5">
         <v>6</v>
       </c>
@@ -10259,13 +12094,19 @@
       <c r="J38" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="K38" s="52" t="s">
+      <c r="K38" s="49" t="s">
+        <v>744</v>
+      </c>
+      <c r="L38" s="45" t="s">
         <v>517</v>
       </c>
-      <c r="L38"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B39" s="47"/>
+      <c r="M38" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N38"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B39" s="53"/>
       <c r="C39" s="5">
         <v>7</v>
       </c>
@@ -10290,13 +12131,19 @@
       <c r="J39" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="K39" s="52" t="s">
+      <c r="K39" s="49" t="s">
+        <v>745</v>
+      </c>
+      <c r="L39" s="45" t="s">
         <v>519</v>
       </c>
-      <c r="L39"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B40" s="47"/>
+      <c r="M39" s="49" t="s">
+        <v>554</v>
+      </c>
+      <c r="N39"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B40" s="53"/>
       <c r="C40" s="5">
         <v>8</v>
       </c>
@@ -10321,13 +12168,19 @@
       <c r="J40" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="K40" s="52" t="s">
+      <c r="K40" s="49" t="s">
+        <v>746</v>
+      </c>
+      <c r="L40" s="45" t="s">
         <v>521</v>
       </c>
-      <c r="L40"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B41" s="47"/>
+      <c r="M40" s="49" t="s">
+        <v>549</v>
+      </c>
+      <c r="N40"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B41" s="53"/>
       <c r="C41" s="5">
         <v>9</v>
       </c>
@@ -10352,13 +12205,19 @@
       <c r="J41" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="K41" s="52" t="s">
+      <c r="K41" s="49" t="s">
+        <v>747</v>
+      </c>
+      <c r="L41" s="45" t="s">
         <v>522</v>
       </c>
-      <c r="L41"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="48"/>
+      <c r="M41" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N41"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B42" s="54"/>
       <c r="C42" s="9">
         <v>10</v>
       </c>
@@ -10383,13 +12242,19 @@
       <c r="J42" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="K42" s="53" t="s">
+      <c r="K42" s="10" t="s">
+        <v>748</v>
+      </c>
+      <c r="L42" s="46" t="s">
         <v>523</v>
       </c>
-      <c r="L42"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="49">
+      <c r="M42" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N42"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B43" s="55">
         <v>5</v>
       </c>
       <c r="C43" s="12">
@@ -10416,13 +12281,19 @@
       <c r="J43" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="K43" s="54" t="s">
+      <c r="K43" s="13" t="s">
+        <v>749</v>
+      </c>
+      <c r="L43" s="47" t="s">
         <v>525</v>
       </c>
-      <c r="L43"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B44" s="47"/>
+      <c r="M43" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N43"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B44" s="53"/>
       <c r="C44" s="5">
         <v>2</v>
       </c>
@@ -10447,13 +12318,19 @@
       <c r="J44" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="K44" s="52" t="s">
+      <c r="K44" s="49" t="s">
+        <v>750</v>
+      </c>
+      <c r="L44" s="45" t="s">
         <v>527</v>
       </c>
-      <c r="L44"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B45" s="47"/>
+      <c r="M44" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N44"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B45" s="53"/>
       <c r="C45" s="5">
         <v>3</v>
       </c>
@@ -10478,13 +12355,19 @@
       <c r="J45" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="K45" s="52" t="s">
+      <c r="K45" s="49" t="s">
+        <v>751</v>
+      </c>
+      <c r="L45" s="45" t="s">
         <v>529</v>
       </c>
-      <c r="L45"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B46" s="47"/>
+      <c r="M45" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="N45"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B46" s="53"/>
       <c r="C46" s="5">
         <v>4</v>
       </c>
@@ -10509,13 +12392,19 @@
       <c r="J46" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="K46" s="52" t="s">
+      <c r="K46" s="49" t="s">
+        <v>752</v>
+      </c>
+      <c r="L46" s="45" t="s">
         <v>532</v>
       </c>
-      <c r="L46"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B47" s="47"/>
+      <c r="M46" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="N46"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B47" s="53"/>
       <c r="C47" s="21">
         <v>5</v>
       </c>
@@ -10540,13 +12429,19 @@
       <c r="J47" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="K47" s="52" t="s">
+      <c r="K47" s="49" t="s">
+        <v>753</v>
+      </c>
+      <c r="L47" s="45" t="s">
         <v>535</v>
       </c>
-      <c r="L47"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B48" s="47"/>
+      <c r="M47" s="49" t="s">
+        <v>547</v>
+      </c>
+      <c r="N47"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B48" s="53"/>
       <c r="C48" s="5">
         <v>6</v>
       </c>
@@ -10571,13 +12466,19 @@
       <c r="J48" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="K48" s="52" t="s">
+      <c r="K48" s="49" t="s">
+        <v>754</v>
+      </c>
+      <c r="L48" s="45" t="s">
         <v>538</v>
       </c>
-      <c r="L48"/>
-    </row>
-    <row r="49" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B49" s="47"/>
+      <c r="M48" s="49" t="s">
+        <v>555</v>
+      </c>
+      <c r="N48"/>
+    </row>
+    <row r="49" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B49" s="53"/>
       <c r="C49" s="5">
         <v>7</v>
       </c>
@@ -10602,13 +12503,19 @@
       <c r="J49" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="K49" s="52" t="s">
+      <c r="K49" s="49" t="s">
+        <v>755</v>
+      </c>
+      <c r="L49" s="45" t="s">
         <v>540</v>
       </c>
-      <c r="L49"/>
-    </row>
-    <row r="50" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B50" s="47"/>
+      <c r="M49" s="49" t="s">
+        <v>548</v>
+      </c>
+      <c r="N49"/>
+    </row>
+    <row r="50" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B50" s="53"/>
       <c r="C50" s="5">
         <v>8</v>
       </c>
@@ -10633,13 +12540,19 @@
       <c r="J50" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="K50" s="52" t="s">
+      <c r="K50" s="49" t="s">
+        <v>756</v>
+      </c>
+      <c r="L50" s="45" t="s">
         <v>542</v>
       </c>
-      <c r="L50"/>
-    </row>
-    <row r="51" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B51" s="47"/>
+      <c r="M50" s="49" t="s">
+        <v>552</v>
+      </c>
+      <c r="N50"/>
+    </row>
+    <row r="51" spans="2:14" x14ac:dyDescent="0.35">
+      <c r="B51" s="53"/>
       <c r="C51" s="5">
         <v>9</v>
       </c>
@@ -10664,13 +12577,19 @@
       <c r="J51" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K51" s="52" t="s">
+      <c r="K51" s="49" t="s">
+        <v>757</v>
+      </c>
+      <c r="L51" s="45" t="s">
         <v>544</v>
       </c>
-      <c r="L51"/>
-    </row>
-    <row r="52" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="50"/>
+      <c r="M51" s="49" t="s">
+        <v>557</v>
+      </c>
+      <c r="N51"/>
+    </row>
+    <row r="52" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B52" s="56"/>
       <c r="C52" s="5">
         <v>10</v>
       </c>
@@ -10695,426 +12614,432 @@
       <c r="J52" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="K52" s="55" t="s">
+      <c r="K52" s="15" t="s">
+        <v>758</v>
+      </c>
+      <c r="L52" s="48" t="s">
         <v>546</v>
       </c>
-      <c r="L52"/>
-    </row>
-    <row r="53" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="M52" s="49" t="s">
+        <v>551</v>
+      </c>
+      <c r="N52"/>
+    </row>
+    <row r="53" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="C53" s="20"/>
-      <c r="L53" s="17"/>
-    </row>
-    <row r="54" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="N53" s="17"/>
+    </row>
+    <row r="54" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C54"/>
       <c r="D54"/>
       <c r="E54"/>
       <c r="F54"/>
     </row>
-    <row r="55" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.35">
       <c r="C55"/>
       <c r="D55"/>
       <c r="E55"/>
       <c r="F55"/>
     </row>
-    <row r="56" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B56" s="19"/>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
       <c r="E56" s="19"/>
       <c r="F56" s="19"/>
     </row>
-    <row r="57" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B57" s="19"/>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
       <c r="E57" s="19"/>
       <c r="F57" s="19"/>
     </row>
-    <row r="58" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
       <c r="E58" s="19"/>
       <c r="F58" s="19"/>
     </row>
-    <row r="59" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
       <c r="D59" s="19"/>
       <c r="E59" s="19"/>
       <c r="F59" s="19"/>
     </row>
-    <row r="60" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
       <c r="D60" s="19"/>
       <c r="E60" s="19"/>
       <c r="F60" s="19"/>
     </row>
-    <row r="61" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
       <c r="D61" s="19"/>
       <c r="E61" s="19"/>
       <c r="F61" s="19"/>
     </row>
-    <row r="62" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
       <c r="D62" s="19"/>
       <c r="E62" s="19"/>
       <c r="F62" s="19"/>
     </row>
-    <row r="63" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
       <c r="D63" s="19"/>
       <c r="E63" s="19"/>
       <c r="F63" s="19"/>
     </row>
-    <row r="64" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
       <c r="D64" s="19"/>
       <c r="E64" s="19"/>
       <c r="F64" s="19"/>
-      <c r="L64" s="18"/>
-    </row>
-    <row r="65" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N64" s="18"/>
+    </row>
+    <row r="65" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
       <c r="D65" s="19"/>
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
-      <c r="L65" s="18"/>
-    </row>
-    <row r="66" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N65" s="18"/>
+    </row>
+    <row r="66" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
       <c r="D66" s="19"/>
       <c r="E66" s="19"/>
       <c r="F66" s="19"/>
-      <c r="L66" s="18"/>
-    </row>
-    <row r="67" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N66" s="18"/>
+    </row>
+    <row r="67" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
       <c r="D67" s="19"/>
       <c r="E67" s="19"/>
       <c r="F67" s="19"/>
-      <c r="L67" s="18"/>
-    </row>
-    <row r="68" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N67" s="18"/>
+    </row>
+    <row r="68" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
       <c r="D68" s="19"/>
       <c r="E68" s="19"/>
       <c r="F68" s="19"/>
-      <c r="L68" s="18"/>
-    </row>
-    <row r="69" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N68" s="18"/>
+    </row>
+    <row r="69" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
       <c r="D69" s="19"/>
       <c r="E69" s="19"/>
       <c r="F69" s="19"/>
-      <c r="L69" s="18"/>
-    </row>
-    <row r="70" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N69" s="18"/>
+    </row>
+    <row r="70" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B70" s="19"/>
       <c r="C70" s="19"/>
       <c r="D70" s="19"/>
       <c r="E70" s="19"/>
       <c r="F70" s="19"/>
-      <c r="L70" s="18"/>
-    </row>
-    <row r="71" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N70" s="18"/>
+    </row>
+    <row r="71" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B71" s="19"/>
       <c r="C71" s="19"/>
       <c r="D71" s="19"/>
       <c r="E71" s="19"/>
       <c r="F71" s="19"/>
-      <c r="L71" s="18"/>
-    </row>
-    <row r="72" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N71" s="18"/>
+    </row>
+    <row r="72" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
       <c r="D72" s="19"/>
       <c r="E72" s="19"/>
       <c r="F72" s="19"/>
-      <c r="L72" s="18"/>
-    </row>
-    <row r="73" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N72" s="18"/>
+    </row>
+    <row r="73" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
       <c r="D73" s="19"/>
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
-      <c r="L73" s="18"/>
-    </row>
-    <row r="74" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N73" s="18"/>
+    </row>
+    <row r="74" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B74" s="19"/>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
       <c r="F74" s="19"/>
-      <c r="L74" s="18"/>
-    </row>
-    <row r="75" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N74" s="18"/>
+    </row>
+    <row r="75" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B75" s="19"/>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
       <c r="E75" s="19"/>
       <c r="F75" s="19"/>
-      <c r="L75" s="18"/>
-    </row>
-    <row r="76" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N75" s="18"/>
+    </row>
+    <row r="76" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B76" s="19"/>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
       <c r="E76" s="19"/>
       <c r="F76" s="19"/>
-      <c r="L76" s="18"/>
-    </row>
-    <row r="77" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N76" s="18"/>
+    </row>
+    <row r="77" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B77" s="19"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="19"/>
       <c r="F77" s="19"/>
-      <c r="L77" s="18"/>
-    </row>
-    <row r="78" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N77" s="18"/>
+    </row>
+    <row r="78" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B78" s="19"/>
       <c r="C78" s="19"/>
       <c r="D78" s="19"/>
       <c r="E78" s="19"/>
       <c r="F78" s="19"/>
-      <c r="L78" s="18"/>
-    </row>
-    <row r="79" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N78" s="18"/>
+    </row>
+    <row r="79" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
       <c r="E79" s="19"/>
       <c r="F79" s="19"/>
-      <c r="L79" s="18"/>
-    </row>
-    <row r="80" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N79" s="18"/>
+    </row>
+    <row r="80" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
       <c r="D80" s="19"/>
       <c r="E80" s="19"/>
       <c r="F80" s="19"/>
-      <c r="L80" s="18"/>
-    </row>
-    <row r="81" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N80" s="18"/>
+    </row>
+    <row r="81" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
       <c r="E81" s="19"/>
       <c r="F81" s="19"/>
-      <c r="L81" s="18"/>
-    </row>
-    <row r="82" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N81" s="18"/>
+    </row>
+    <row r="82" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
       <c r="E82" s="19"/>
       <c r="F82" s="19"/>
-      <c r="L82" s="18"/>
-    </row>
-    <row r="83" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N82" s="18"/>
+    </row>
+    <row r="83" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
       <c r="E83" s="19"/>
       <c r="F83" s="19"/>
-      <c r="L83" s="18"/>
-    </row>
-    <row r="84" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N83" s="18"/>
+    </row>
+    <row r="84" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
-      <c r="L84" s="18"/>
-    </row>
-    <row r="85" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N84" s="18"/>
+    </row>
+    <row r="85" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
       <c r="E85" s="19"/>
       <c r="F85" s="19"/>
-      <c r="L85" s="18"/>
-    </row>
-    <row r="86" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N85" s="18"/>
+    </row>
+    <row r="86" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
       <c r="E86" s="19"/>
       <c r="F86" s="19"/>
-      <c r="L86" s="18"/>
-    </row>
-    <row r="87" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N86" s="18"/>
+    </row>
+    <row r="87" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
       <c r="D87" s="19"/>
       <c r="E87" s="19"/>
       <c r="F87" s="19"/>
-      <c r="L87" s="18"/>
-    </row>
-    <row r="88" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N87" s="18"/>
+    </row>
+    <row r="88" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
       <c r="D88" s="19"/>
       <c r="E88" s="19"/>
       <c r="F88" s="19"/>
-      <c r="L88" s="18"/>
-    </row>
-    <row r="89" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N88" s="18"/>
+    </row>
+    <row r="89" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
       <c r="D89" s="19"/>
       <c r="E89" s="19"/>
       <c r="F89" s="19"/>
-      <c r="L89" s="18"/>
-    </row>
-    <row r="90" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N89" s="18"/>
+    </row>
+    <row r="90" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
       <c r="D90" s="19"/>
       <c r="E90" s="19"/>
       <c r="F90" s="19"/>
-      <c r="L90" s="18"/>
-    </row>
-    <row r="91" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N90" s="18"/>
+    </row>
+    <row r="91" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
       <c r="D91" s="19"/>
       <c r="E91" s="19"/>
       <c r="F91" s="19"/>
-      <c r="L91" s="18"/>
-    </row>
-    <row r="92" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N91" s="18"/>
+    </row>
+    <row r="92" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
       <c r="D92" s="19"/>
       <c r="E92" s="19"/>
       <c r="F92" s="19"/>
-      <c r="L92" s="18"/>
-    </row>
-    <row r="93" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N92" s="18"/>
+    </row>
+    <row r="93" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B93" s="19"/>
       <c r="C93" s="19"/>
       <c r="D93" s="19"/>
       <c r="E93" s="19"/>
       <c r="F93" s="19"/>
-      <c r="L93" s="18"/>
-    </row>
-    <row r="94" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N93" s="18"/>
+    </row>
+    <row r="94" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B94" s="19"/>
       <c r="C94" s="19"/>
       <c r="D94" s="19"/>
       <c r="E94" s="19"/>
       <c r="F94" s="19"/>
-      <c r="L94" s="18"/>
-    </row>
-    <row r="95" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N94" s="18"/>
+    </row>
+    <row r="95" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B95" s="19"/>
       <c r="C95" s="19"/>
       <c r="D95" s="19"/>
       <c r="E95" s="19"/>
       <c r="F95" s="19"/>
-      <c r="L95" s="18"/>
-    </row>
-    <row r="96" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N95" s="18"/>
+    </row>
+    <row r="96" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
       <c r="D96" s="19"/>
       <c r="E96" s="19"/>
       <c r="F96" s="19"/>
-      <c r="L96" s="18"/>
-    </row>
-    <row r="97" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N96" s="18"/>
+    </row>
+    <row r="97" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
       <c r="D97" s="19"/>
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
-      <c r="L97" s="18"/>
-    </row>
-    <row r="98" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N97" s="18"/>
+    </row>
+    <row r="98" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B98" s="19"/>
       <c r="C98" s="19"/>
       <c r="D98" s="19"/>
       <c r="E98" s="19"/>
       <c r="F98" s="19"/>
-      <c r="L98" s="18"/>
-    </row>
-    <row r="99" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N98" s="18"/>
+    </row>
+    <row r="99" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
       <c r="D99" s="19"/>
       <c r="E99" s="19"/>
       <c r="F99" s="19"/>
-      <c r="L99" s="18"/>
-    </row>
-    <row r="100" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N99" s="18"/>
+    </row>
+    <row r="100" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B100" s="19"/>
       <c r="C100" s="19"/>
       <c r="D100" s="19"/>
       <c r="E100" s="19"/>
       <c r="F100" s="19"/>
-      <c r="L100" s="18"/>
-    </row>
-    <row r="101" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N100" s="18"/>
+    </row>
+    <row r="101" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B101" s="19"/>
       <c r="C101" s="19"/>
       <c r="D101" s="19"/>
       <c r="E101" s="19"/>
       <c r="F101" s="19"/>
-      <c r="L101" s="18"/>
-    </row>
-    <row r="102" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N101" s="18"/>
+    </row>
+    <row r="102" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B102" s="19"/>
       <c r="C102" s="19"/>
       <c r="D102" s="19"/>
       <c r="E102" s="19"/>
       <c r="F102" s="19"/>
-      <c r="L102" s="18"/>
-    </row>
-    <row r="103" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N102" s="18"/>
+    </row>
+    <row r="103" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B103" s="19"/>
       <c r="C103" s="19"/>
       <c r="D103" s="19"/>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
-      <c r="L103" s="18"/>
-    </row>
-    <row r="104" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N103" s="18"/>
+    </row>
+    <row r="104" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B104" s="19"/>
       <c r="C104" s="19"/>
       <c r="D104" s="19"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
-      <c r="L104" s="18"/>
-    </row>
-    <row r="105" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N104" s="18"/>
+    </row>
+    <row r="105" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B105" s="19"/>
       <c r="C105" s="19"/>
       <c r="D105" s="19"/>
       <c r="E105" s="19"/>
       <c r="F105" s="19"/>
-      <c r="L105" s="18"/>
-    </row>
-    <row r="106" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="N105" s="18"/>
+    </row>
+    <row r="106" spans="2:14" s="3" customFormat="1" x14ac:dyDescent="0.35">
       <c r="B106" s="19"/>
       <c r="C106" s="19"/>
       <c r="D106" s="19"/>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
-      <c r="L106" s="18"/>
+      <c r="N106" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">
